--- a/workbooks/00 Review Deck.xlsx
+++ b/workbooks/00 Review Deck.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="1263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="1281">
   <si>
     <t>Challenge</t>
   </si>
@@ -1087,12 +1087,21 @@
     <t>"</t>
   </si>
   <si>
+    <t>DOUBLEQUOTE</t>
+  </si>
+  <si>
     <t>DOUBLEQUOTES</t>
   </si>
   <si>
+    <t>QUOTATIONMARK</t>
+  </si>
+  <si>
     <t>QUOTATIONMARKS</t>
   </si>
   <si>
+    <t>QUOTE</t>
+  </si>
+  <si>
     <t>QUOTES</t>
   </si>
   <si>
@@ -1288,9 +1297,24 @@
     <t>A test that is always true.</t>
   </si>
   <si>
+    <t>=TRUE</t>
+  </si>
+  <si>
+    <t>=TRUE(</t>
+  </si>
+  <si>
+    <t>=TRUE()</t>
+  </si>
+  <si>
     <t>TRUE</t>
   </si>
   <si>
+    <t>TRUE(</t>
+  </si>
+  <si>
+    <t>TRUE()</t>
+  </si>
+  <si>
     <t>In IFS, what do you put as the last test to catch all remaining cases?</t>
   </si>
   <si>
@@ -2602,9 +2626,24 @@
     <t>0</t>
   </si>
   <si>
+    <t>=FALSE</t>
+  </si>
+  <si>
+    <t>=FALSE(</t>
+  </si>
+  <si>
+    <t>=FALSE()</t>
+  </si>
+  <si>
     <t>FALSE</t>
   </si>
   <si>
+    <t>FALSE(</t>
+  </si>
+  <si>
+    <t>FALSE()</t>
+  </si>
+  <si>
     <t>Which 4th argument makes VLOOKUP find an exact match?</t>
   </si>
   <si>
@@ -2671,6 +2710,24 @@
     <t>The position finder.</t>
   </si>
   <si>
+    <t>=XMATCH</t>
+  </si>
+  <si>
+    <t>=XMATCH(</t>
+  </si>
+  <si>
+    <t>=XMATCH()</t>
+  </si>
+  <si>
+    <t>XMATCH</t>
+  </si>
+  <si>
+    <t>XMATCH(</t>
+  </si>
+  <si>
+    <t>XMATCH()</t>
+  </si>
+  <si>
     <t>Which function goes inside INDEX to find the row position?</t>
   </si>
   <si>
@@ -2680,24 +2737,6 @@
     <t>X plus MATCH.</t>
   </si>
   <si>
-    <t>=XMATCH</t>
-  </si>
-  <si>
-    <t>=XMATCH(</t>
-  </si>
-  <si>
-    <t>=XMATCH()</t>
-  </si>
-  <si>
-    <t>XMATCH</t>
-  </si>
-  <si>
-    <t>XMATCH(</t>
-  </si>
-  <si>
-    <t>XMATCH()</t>
-  </si>
-  <si>
     <t>Which modern function returns a position with an exact match by default?</t>
   </si>
   <si>
@@ -3532,6 +3571,21 @@
     <t>#SPILL!</t>
   </si>
   <si>
+    <t>=SPILL</t>
+  </si>
+  <si>
+    <t>=SPILL(</t>
+  </si>
+  <si>
+    <t>=SPILL()</t>
+  </si>
+  <si>
+    <t>SPILL(</t>
+  </si>
+  <si>
+    <t>SPILL()</t>
+  </si>
+  <si>
     <t>Which error appears when a spill range is blocked?</t>
   </si>
   <si>
@@ -3823,7 +3877,7 @@
     <t>3 · Set Box to the Suggested box (select the Box cell, press Alt+↓, pick the number).</t>
   </si>
   <si>
-    <t>4 · Select Last reviewed and press Ctrl+; to stamp today's date.</t>
+    <t>4 · Select Last reviewed and press Ctrl+; to stamp today's date (Suggested box then says done today).</t>
   </si>
   <si>
     <t>5 · Clear your answers (select them, press Delete), then clear the filter (Alt+↓ → Select All).</t>
@@ -4528,7 +4582,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1237</v>
+        <v>1255</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4540,12 +4594,12 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>1238</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -4557,7 +4611,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>1239</v>
+        <v>1257</v>
       </c>
       <c r="B5" s="6" cm="1">
         <f t="array" ref="B5">COUNTIF(Deck!$K$5:$K$178,"DUE")</f>
@@ -4566,7 +4620,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="5" t="s">
-        <v>1240</v>
+        <v>1258</v>
       </c>
       <c r="B6" s="6" cm="1">
         <f t="array" ref="B6">COUNTIF(Deck!$K$5:$K$178,"NEW")</f>
@@ -4575,7 +4629,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="5" t="s">
-        <v>1241</v>
+        <v>1259</v>
       </c>
       <c r="B7" s="6" cm="1">
         <f t="array" ref="B7">COUNTIF(Deck!$H$5:$H$178,5)</f>
@@ -4584,7 +4638,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>1242</v>
+        <v>1260</v>
       </c>
       <c r="B8" s="6" cm="1" t="str">
         <f t="array" ref="B8">TEXT(B7/174,"0%")</f>
@@ -4593,7 +4647,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>1243</v>
+        <v>1261</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -4608,12 +4662,12 @@
         <v>13</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1244</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="8" t="s">
-        <v>1245</v>
+        <v>1263</v>
       </c>
       <c r="B12" s="9" cm="1">
         <f t="array" ref="B12">COUNTIF(Deck!$K$5:$K$178,"NEW")</f>
@@ -4622,7 +4676,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="8" t="s">
-        <v>1246</v>
+        <v>1264</v>
       </c>
       <c r="B13" s="9" cm="1">
         <f t="array" ref="B13">COUNTIF(Deck!$H$5:$H$178,1)</f>
@@ -4631,7 +4685,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="8" t="s">
-        <v>1247</v>
+        <v>1265</v>
       </c>
       <c r="B14" s="9" cm="1">
         <f t="array" ref="B14">COUNTIF(Deck!$H$5:$H$178,2)</f>
@@ -4640,7 +4694,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="8" t="s">
-        <v>1248</v>
+        <v>1266</v>
       </c>
       <c r="B15" s="9" cm="1">
         <f t="array" ref="B15">COUNTIF(Deck!$H$5:$H$178,3)</f>
@@ -4649,7 +4703,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="8" t="s">
-        <v>1249</v>
+        <v>1267</v>
       </c>
       <c r="B16" s="9" cm="1">
         <f t="array" ref="B16">COUNTIF(Deck!$H$5:$H$178,4)</f>
@@ -4658,7 +4712,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="8" t="s">
-        <v>1250</v>
+        <v>1268</v>
       </c>
       <c r="B17" s="9" cm="1">
         <f t="array" ref="B17">COUNTIF(Deck!$H$5:$H$178,5)</f>
@@ -4667,7 +4721,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>1251</v>
+        <v>1269</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -4679,27 +4733,27 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="10" t="s">
-        <v>1252</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="10" t="s">
-        <v>1253</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="10" t="s">
-        <v>1254</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="10" t="s">
-        <v>1255</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>1256</v>
+        <v>1274</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -4711,32 +4765,32 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="10" t="s">
-        <v>1257</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="10" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="10" t="s">
-        <v>1259</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="10" t="s">
-        <v>1260</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="10" t="s">
-        <v>1261</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="10" t="s">
-        <v>1262</v>
+        <v>1280</v>
       </c>
     </row>
   </sheetData>
@@ -4840,7 +4894,7 @@
         <v/>
       </c>
       <c r="G5" s="9" cm="1" t="str">
-        <f t="array" ref="G5">IF(F5="","",IF(LEFT(F5,1)="✔",MIN(IF(H5="",1,H5)+1,5),1))</f>
+        <f t="array" ref="G5">IF(F5="","",IF(I5=TODAY(),"done today",IF(LEFT(F5,1)="✔",MIN(IF(H5="",1,H5)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H5" s="14"/>
@@ -4873,7 +4927,7 @@
         <v/>
       </c>
       <c r="G6" s="9" cm="1" t="str">
-        <f t="array" ref="G6">IF(F6="","",IF(LEFT(F6,1)="✔",MIN(IF(H6="",1,H6)+1,5),1))</f>
+        <f t="array" ref="G6">IF(F6="","",IF(I6=TODAY(),"done today",IF(LEFT(F6,1)="✔",MIN(IF(H6="",1,H6)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H6" s="14"/>
@@ -4906,7 +4960,7 @@
         <v/>
       </c>
       <c r="G7" s="9" cm="1" t="str">
-        <f t="array" ref="G7">IF(F7="","",IF(LEFT(F7,1)="✔",MIN(IF(H7="",1,H7)+1,5),1))</f>
+        <f t="array" ref="G7">IF(F7="","",IF(I7=TODAY(),"done today",IF(LEFT(F7,1)="✔",MIN(IF(H7="",1,H7)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H7" s="14"/>
@@ -4939,7 +4993,7 @@
         <v/>
       </c>
       <c r="G8" s="9" cm="1" t="str">
-        <f t="array" ref="G8">IF(F8="","",IF(LEFT(F8,1)="✔",MIN(IF(H8="",1,H8)+1,5),1))</f>
+        <f t="array" ref="G8">IF(F8="","",IF(I8=TODAY(),"done today",IF(LEFT(F8,1)="✔",MIN(IF(H8="",1,H8)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H8" s="14"/>
@@ -4972,7 +5026,7 @@
         <v/>
       </c>
       <c r="G9" s="9" cm="1" t="str">
-        <f t="array" ref="G9">IF(F9="","",IF(LEFT(F9,1)="✔",MIN(IF(H9="",1,H9)+1,5),1))</f>
+        <f t="array" ref="G9">IF(F9="","",IF(I9=TODAY(),"done today",IF(LEFT(F9,1)="✔",MIN(IF(H9="",1,H9)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H9" s="14"/>
@@ -5005,7 +5059,7 @@
         <v/>
       </c>
       <c r="G10" s="9" cm="1" t="str">
-        <f t="array" ref="G10">IF(F10="","",IF(LEFT(F10,1)="✔",MIN(IF(H10="",1,H10)+1,5),1))</f>
+        <f t="array" ref="G10">IF(F10="","",IF(I10=TODAY(),"done today",IF(LEFT(F10,1)="✔",MIN(IF(H10="",1,H10)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H10" s="14"/>
@@ -5038,7 +5092,7 @@
         <v/>
       </c>
       <c r="G11" s="9" cm="1" t="str">
-        <f t="array" ref="G11">IF(F11="","",IF(LEFT(F11,1)="✔",MIN(IF(H11="",1,H11)+1,5),1))</f>
+        <f t="array" ref="G11">IF(F11="","",IF(I11=TODAY(),"done today",IF(LEFT(F11,1)="✔",MIN(IF(H11="",1,H11)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H11" s="14"/>
@@ -5071,7 +5125,7 @@
         <v/>
       </c>
       <c r="G12" s="9" cm="1" t="str">
-        <f t="array" ref="G12">IF(F12="","",IF(LEFT(F12,1)="✔",MIN(IF(H12="",1,H12)+1,5),1))</f>
+        <f t="array" ref="G12">IF(F12="","",IF(I12=TODAY(),"done today",IF(LEFT(F12,1)="✔",MIN(IF(H12="",1,H12)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H12" s="14"/>
@@ -5104,7 +5158,7 @@
         <v/>
       </c>
       <c r="G13" s="9" cm="1" t="str">
-        <f t="array" ref="G13">IF(F13="","",IF(LEFT(F13,1)="✔",MIN(IF(H13="",1,H13)+1,5),1))</f>
+        <f t="array" ref="G13">IF(F13="","",IF(I13=TODAY(),"done today",IF(LEFT(F13,1)="✔",MIN(IF(H13="",1,H13)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H13" s="14"/>
@@ -5137,7 +5191,7 @@
         <v/>
       </c>
       <c r="G14" s="9" cm="1" t="str">
-        <f t="array" ref="G14">IF(F14="","",IF(LEFT(F14,1)="✔",MIN(IF(H14="",1,H14)+1,5),1))</f>
+        <f t="array" ref="G14">IF(F14="","",IF(I14=TODAY(),"done today",IF(LEFT(F14,1)="✔",MIN(IF(H14="",1,H14)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H14" s="14"/>
@@ -5170,7 +5224,7 @@
         <v/>
       </c>
       <c r="G15" s="9" cm="1" t="str">
-        <f t="array" ref="G15">IF(F15="","",IF(LEFT(F15,1)="✔",MIN(IF(H15="",1,H15)+1,5),1))</f>
+        <f t="array" ref="G15">IF(F15="","",IF(I15=TODAY(),"done today",IF(LEFT(F15,1)="✔",MIN(IF(H15="",1,H15)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H15" s="14"/>
@@ -5203,7 +5257,7 @@
         <v/>
       </c>
       <c r="G16" s="9" cm="1" t="str">
-        <f t="array" ref="G16">IF(F16="","",IF(LEFT(F16,1)="✔",MIN(IF(H16="",1,H16)+1,5),1))</f>
+        <f t="array" ref="G16">IF(F16="","",IF(I16=TODAY(),"done today",IF(LEFT(F16,1)="✔",MIN(IF(H16="",1,H16)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H16" s="14"/>
@@ -5236,7 +5290,7 @@
         <v/>
       </c>
       <c r="G17" s="9" cm="1" t="str">
-        <f t="array" ref="G17">IF(F17="","",IF(LEFT(F17,1)="✔",MIN(IF(H17="",1,H17)+1,5),1))</f>
+        <f t="array" ref="G17">IF(F17="","",IF(I17=TODAY(),"done today",IF(LEFT(F17,1)="✔",MIN(IF(H17="",1,H17)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H17" s="14"/>
@@ -5269,7 +5323,7 @@
         <v/>
       </c>
       <c r="G18" s="9" cm="1" t="str">
-        <f t="array" ref="G18">IF(F18="","",IF(LEFT(F18,1)="✔",MIN(IF(H18="",1,H18)+1,5),1))</f>
+        <f t="array" ref="G18">IF(F18="","",IF(I18=TODAY(),"done today",IF(LEFT(F18,1)="✔",MIN(IF(H18="",1,H18)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H18" s="14"/>
@@ -5302,7 +5356,7 @@
         <v/>
       </c>
       <c r="G19" s="9" cm="1" t="str">
-        <f t="array" ref="G19">IF(F19="","",IF(LEFT(F19,1)="✔",MIN(IF(H19="",1,H19)+1,5),1))</f>
+        <f t="array" ref="G19">IF(F19="","",IF(I19=TODAY(),"done today",IF(LEFT(F19,1)="✔",MIN(IF(H19="",1,H19)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H19" s="14"/>
@@ -5335,7 +5389,7 @@
         <v/>
       </c>
       <c r="G20" s="9" cm="1" t="str">
-        <f t="array" ref="G20">IF(F20="","",IF(LEFT(F20,1)="✔",MIN(IF(H20="",1,H20)+1,5),1))</f>
+        <f t="array" ref="G20">IF(F20="","",IF(I20=TODAY(),"done today",IF(LEFT(F20,1)="✔",MIN(IF(H20="",1,H20)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H20" s="14"/>
@@ -5368,7 +5422,7 @@
         <v/>
       </c>
       <c r="G21" s="9" cm="1" t="str">
-        <f t="array" ref="G21">IF(F21="","",IF(LEFT(F21,1)="✔",MIN(IF(H21="",1,H21)+1,5),1))</f>
+        <f t="array" ref="G21">IF(F21="","",IF(I21=TODAY(),"done today",IF(LEFT(F21,1)="✔",MIN(IF(H21="",1,H21)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H21" s="14"/>
@@ -5401,7 +5455,7 @@
         <v/>
       </c>
       <c r="G22" s="9" cm="1" t="str">
-        <f t="array" ref="G22">IF(F22="","",IF(LEFT(F22,1)="✔",MIN(IF(H22="",1,H22)+1,5),1))</f>
+        <f t="array" ref="G22">IF(F22="","",IF(I22=TODAY(),"done today",IF(LEFT(F22,1)="✔",MIN(IF(H22="",1,H22)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H22" s="14"/>
@@ -5434,7 +5488,7 @@
         <v/>
       </c>
       <c r="G23" s="9" cm="1" t="str">
-        <f t="array" ref="G23">IF(F23="","",IF(LEFT(F23,1)="✔",MIN(IF(H23="",1,H23)+1,5),1))</f>
+        <f t="array" ref="G23">IF(F23="","",IF(I23=TODAY(),"done today",IF(LEFT(F23,1)="✔",MIN(IF(H23="",1,H23)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H23" s="14"/>
@@ -5467,7 +5521,7 @@
         <v/>
       </c>
       <c r="G24" s="9" cm="1" t="str">
-        <f t="array" ref="G24">IF(F24="","",IF(LEFT(F24,1)="✔",MIN(IF(H24="",1,H24)+1,5),1))</f>
+        <f t="array" ref="G24">IF(F24="","",IF(I24=TODAY(),"done today",IF(LEFT(F24,1)="✔",MIN(IF(H24="",1,H24)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H24" s="14"/>
@@ -5500,7 +5554,7 @@
         <v/>
       </c>
       <c r="G25" s="9" cm="1" t="str">
-        <f t="array" ref="G25">IF(F25="","",IF(LEFT(F25,1)="✔",MIN(IF(H25="",1,H25)+1,5),1))</f>
+        <f t="array" ref="G25">IF(F25="","",IF(I25=TODAY(),"done today",IF(LEFT(F25,1)="✔",MIN(IF(H25="",1,H25)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H25" s="14"/>
@@ -5533,7 +5587,7 @@
         <v/>
       </c>
       <c r="G26" s="9" cm="1" t="str">
-        <f t="array" ref="G26">IF(F26="","",IF(LEFT(F26,1)="✔",MIN(IF(H26="",1,H26)+1,5),1))</f>
+        <f t="array" ref="G26">IF(F26="","",IF(I26=TODAY(),"done today",IF(LEFT(F26,1)="✔",MIN(IF(H26="",1,H26)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H26" s="14"/>
@@ -5566,7 +5620,7 @@
         <v/>
       </c>
       <c r="G27" s="9" cm="1" t="str">
-        <f t="array" ref="G27">IF(F27="","",IF(LEFT(F27,1)="✔",MIN(IF(H27="",1,H27)+1,5),1))</f>
+        <f t="array" ref="G27">IF(F27="","",IF(I27=TODAY(),"done today",IF(LEFT(F27,1)="✔",MIN(IF(H27="",1,H27)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H27" s="14"/>
@@ -5599,7 +5653,7 @@
         <v/>
       </c>
       <c r="G28" s="9" cm="1" t="str">
-        <f t="array" ref="G28">IF(F28="","",IF(LEFT(F28,1)="✔",MIN(IF(H28="",1,H28)+1,5),1))</f>
+        <f t="array" ref="G28">IF(F28="","",IF(I28=TODAY(),"done today",IF(LEFT(F28,1)="✔",MIN(IF(H28="",1,H28)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H28" s="14"/>
@@ -5632,7 +5686,7 @@
         <v/>
       </c>
       <c r="G29" s="9" cm="1" t="str">
-        <f t="array" ref="G29">IF(F29="","",IF(LEFT(F29,1)="✔",MIN(IF(H29="",1,H29)+1,5),1))</f>
+        <f t="array" ref="G29">IF(F29="","",IF(I29=TODAY(),"done today",IF(LEFT(F29,1)="✔",MIN(IF(H29="",1,H29)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H29" s="14"/>
@@ -5665,7 +5719,7 @@
         <v/>
       </c>
       <c r="G30" s="9" cm="1" t="str">
-        <f t="array" ref="G30">IF(F30="","",IF(LEFT(F30,1)="✔",MIN(IF(H30="",1,H30)+1,5),1))</f>
+        <f t="array" ref="G30">IF(F30="","",IF(I30=TODAY(),"done today",IF(LEFT(F30,1)="✔",MIN(IF(H30="",1,H30)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H30" s="14"/>
@@ -5698,7 +5752,7 @@
         <v/>
       </c>
       <c r="G31" s="9" cm="1" t="str">
-        <f t="array" ref="G31">IF(F31="","",IF(LEFT(F31,1)="✔",MIN(IF(H31="",1,H31)+1,5),1))</f>
+        <f t="array" ref="G31">IF(F31="","",IF(I31=TODAY(),"done today",IF(LEFT(F31,1)="✔",MIN(IF(H31="",1,H31)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H31" s="14"/>
@@ -5731,7 +5785,7 @@
         <v/>
       </c>
       <c r="G32" s="9" cm="1" t="str">
-        <f t="array" ref="G32">IF(F32="","",IF(LEFT(F32,1)="✔",MIN(IF(H32="",1,H32)+1,5),1))</f>
+        <f t="array" ref="G32">IF(F32="","",IF(I32=TODAY(),"done today",IF(LEFT(F32,1)="✔",MIN(IF(H32="",1,H32)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H32" s="14"/>
@@ -5764,7 +5818,7 @@
         <v/>
       </c>
       <c r="G33" s="9" cm="1" t="str">
-        <f t="array" ref="G33">IF(F33="","",IF(LEFT(F33,1)="✔",MIN(IF(H33="",1,H33)+1,5),1))</f>
+        <f t="array" ref="G33">IF(F33="","",IF(I33=TODAY(),"done today",IF(LEFT(F33,1)="✔",MIN(IF(H33="",1,H33)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H33" s="14"/>
@@ -5797,7 +5851,7 @@
         <v/>
       </c>
       <c r="G34" s="9" cm="1" t="str">
-        <f t="array" ref="G34">IF(F34="","",IF(LEFT(F34,1)="✔",MIN(IF(H34="",1,H34)+1,5),1))</f>
+        <f t="array" ref="G34">IF(F34="","",IF(I34=TODAY(),"done today",IF(LEFT(F34,1)="✔",MIN(IF(H34="",1,H34)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H34" s="14"/>
@@ -5830,7 +5884,7 @@
         <v/>
       </c>
       <c r="G35" s="9" cm="1" t="str">
-        <f t="array" ref="G35">IF(F35="","",IF(LEFT(F35,1)="✔",MIN(IF(H35="",1,H35)+1,5),1))</f>
+        <f t="array" ref="G35">IF(F35="","",IF(I35=TODAY(),"done today",IF(LEFT(F35,1)="✔",MIN(IF(H35="",1,H35)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H35" s="14"/>
@@ -5863,7 +5917,7 @@
         <v/>
       </c>
       <c r="G36" s="9" cm="1" t="str">
-        <f t="array" ref="G36">IF(F36="","",IF(LEFT(F36,1)="✔",MIN(IF(H36="",1,H36)+1,5),1))</f>
+        <f t="array" ref="G36">IF(F36="","",IF(I36=TODAY(),"done today",IF(LEFT(F36,1)="✔",MIN(IF(H36="",1,H36)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H36" s="14"/>
@@ -5896,7 +5950,7 @@
         <v/>
       </c>
       <c r="G37" s="9" cm="1" t="str">
-        <f t="array" ref="G37">IF(F37="","",IF(LEFT(F37,1)="✔",MIN(IF(H37="",1,H37)+1,5),1))</f>
+        <f t="array" ref="G37">IF(F37="","",IF(I37=TODAY(),"done today",IF(LEFT(F37,1)="✔",MIN(IF(H37="",1,H37)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H37" s="14"/>
@@ -5929,7 +5983,7 @@
         <v/>
       </c>
       <c r="G38" s="9" cm="1" t="str">
-        <f t="array" ref="G38">IF(F38="","",IF(LEFT(F38,1)="✔",MIN(IF(H38="",1,H38)+1,5),1))</f>
+        <f t="array" ref="G38">IF(F38="","",IF(I38=TODAY(),"done today",IF(LEFT(F38,1)="✔",MIN(IF(H38="",1,H38)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H38" s="14"/>
@@ -5962,7 +6016,7 @@
         <v/>
       </c>
       <c r="G39" s="9" cm="1" t="str">
-        <f t="array" ref="G39">IF(F39="","",IF(LEFT(F39,1)="✔",MIN(IF(H39="",1,H39)+1,5),1))</f>
+        <f t="array" ref="G39">IF(F39="","",IF(I39=TODAY(),"done today",IF(LEFT(F39,1)="✔",MIN(IF(H39="",1,H39)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H39" s="14"/>
@@ -5995,7 +6049,7 @@
         <v/>
       </c>
       <c r="G40" s="9" cm="1" t="str">
-        <f t="array" ref="G40">IF(F40="","",IF(LEFT(F40,1)="✔",MIN(IF(H40="",1,H40)+1,5),1))</f>
+        <f t="array" ref="G40">IF(F40="","",IF(I40=TODAY(),"done today",IF(LEFT(F40,1)="✔",MIN(IF(H40="",1,H40)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H40" s="14"/>
@@ -6028,7 +6082,7 @@
         <v/>
       </c>
       <c r="G41" s="9" cm="1" t="str">
-        <f t="array" ref="G41">IF(F41="","",IF(LEFT(F41,1)="✔",MIN(IF(H41="",1,H41)+1,5),1))</f>
+        <f t="array" ref="G41">IF(F41="","",IF(I41=TODAY(),"done today",IF(LEFT(F41,1)="✔",MIN(IF(H41="",1,H41)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H41" s="14"/>
@@ -6061,7 +6115,7 @@
         <v/>
       </c>
       <c r="G42" s="9" cm="1" t="str">
-        <f t="array" ref="G42">IF(F42="","",IF(LEFT(F42,1)="✔",MIN(IF(H42="",1,H42)+1,5),1))</f>
+        <f t="array" ref="G42">IF(F42="","",IF(I42=TODAY(),"done today",IF(LEFT(F42,1)="✔",MIN(IF(H42="",1,H42)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H42" s="14"/>
@@ -6094,7 +6148,7 @@
         <v/>
       </c>
       <c r="G43" s="9" cm="1" t="str">
-        <f t="array" ref="G43">IF(F43="","",IF(LEFT(F43,1)="✔",MIN(IF(H43="",1,H43)+1,5),1))</f>
+        <f t="array" ref="G43">IF(F43="","",IF(I43=TODAY(),"done today",IF(LEFT(F43,1)="✔",MIN(IF(H43="",1,H43)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H43" s="14"/>
@@ -6127,7 +6181,7 @@
         <v/>
       </c>
       <c r="G44" s="9" cm="1" t="str">
-        <f t="array" ref="G44">IF(F44="","",IF(LEFT(F44,1)="✔",MIN(IF(H44="",1,H44)+1,5),1))</f>
+        <f t="array" ref="G44">IF(F44="","",IF(I44=TODAY(),"done today",IF(LEFT(F44,1)="✔",MIN(IF(H44="",1,H44)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H44" s="14"/>
@@ -6160,7 +6214,7 @@
         <v/>
       </c>
       <c r="G45" s="9" cm="1" t="str">
-        <f t="array" ref="G45">IF(F45="","",IF(LEFT(F45,1)="✔",MIN(IF(H45="",1,H45)+1,5),1))</f>
+        <f t="array" ref="G45">IF(F45="","",IF(I45=TODAY(),"done today",IF(LEFT(F45,1)="✔",MIN(IF(H45="",1,H45)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H45" s="14"/>
@@ -6193,7 +6247,7 @@
         <v/>
       </c>
       <c r="G46" s="9" cm="1" t="str">
-        <f t="array" ref="G46">IF(F46="","",IF(LEFT(F46,1)="✔",MIN(IF(H46="",1,H46)+1,5),1))</f>
+        <f t="array" ref="G46">IF(F46="","",IF(I46=TODAY(),"done today",IF(LEFT(F46,1)="✔",MIN(IF(H46="",1,H46)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H46" s="14"/>
@@ -6226,7 +6280,7 @@
         <v/>
       </c>
       <c r="G47" s="9" cm="1" t="str">
-        <f t="array" ref="G47">IF(F47="","",IF(LEFT(F47,1)="✔",MIN(IF(H47="",1,H47)+1,5),1))</f>
+        <f t="array" ref="G47">IF(F47="","",IF(I47=TODAY(),"done today",IF(LEFT(F47,1)="✔",MIN(IF(H47="",1,H47)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H47" s="14"/>
@@ -6259,7 +6313,7 @@
         <v/>
       </c>
       <c r="G48" s="9" cm="1" t="str">
-        <f t="array" ref="G48">IF(F48="","",IF(LEFT(F48,1)="✔",MIN(IF(H48="",1,H48)+1,5),1))</f>
+        <f t="array" ref="G48">IF(F48="","",IF(I48=TODAY(),"done today",IF(LEFT(F48,1)="✔",MIN(IF(H48="",1,H48)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H48" s="14"/>
@@ -6292,7 +6346,7 @@
         <v/>
       </c>
       <c r="G49" s="9" cm="1" t="str">
-        <f t="array" ref="G49">IF(F49="","",IF(LEFT(F49,1)="✔",MIN(IF(H49="",1,H49)+1,5),1))</f>
+        <f t="array" ref="G49">IF(F49="","",IF(I49=TODAY(),"done today",IF(LEFT(F49,1)="✔",MIN(IF(H49="",1,H49)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H49" s="14"/>
@@ -6325,7 +6379,7 @@
         <v/>
       </c>
       <c r="G50" s="9" cm="1" t="str">
-        <f t="array" ref="G50">IF(F50="","",IF(LEFT(F50,1)="✔",MIN(IF(H50="",1,H50)+1,5),1))</f>
+        <f t="array" ref="G50">IF(F50="","",IF(I50=TODAY(),"done today",IF(LEFT(F50,1)="✔",MIN(IF(H50="",1,H50)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H50" s="14"/>
@@ -6358,7 +6412,7 @@
         <v/>
       </c>
       <c r="G51" s="9" cm="1" t="str">
-        <f t="array" ref="G51">IF(F51="","",IF(LEFT(F51,1)="✔",MIN(IF(H51="",1,H51)+1,5),1))</f>
+        <f t="array" ref="G51">IF(F51="","",IF(I51=TODAY(),"done today",IF(LEFT(F51,1)="✔",MIN(IF(H51="",1,H51)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H51" s="14"/>
@@ -6391,7 +6445,7 @@
         <v/>
       </c>
       <c r="G52" s="9" cm="1" t="str">
-        <f t="array" ref="G52">IF(F52="","",IF(LEFT(F52,1)="✔",MIN(IF(H52="",1,H52)+1,5),1))</f>
+        <f t="array" ref="G52">IF(F52="","",IF(I52=TODAY(),"done today",IF(LEFT(F52,1)="✔",MIN(IF(H52="",1,H52)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H52" s="14"/>
@@ -6424,7 +6478,7 @@
         <v/>
       </c>
       <c r="G53" s="9" cm="1" t="str">
-        <f t="array" ref="G53">IF(F53="","",IF(LEFT(F53,1)="✔",MIN(IF(H53="",1,H53)+1,5),1))</f>
+        <f t="array" ref="G53">IF(F53="","",IF(I53=TODAY(),"done today",IF(LEFT(F53,1)="✔",MIN(IF(H53="",1,H53)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H53" s="14"/>
@@ -6457,7 +6511,7 @@
         <v/>
       </c>
       <c r="G54" s="9" cm="1" t="str">
-        <f t="array" ref="G54">IF(F54="","",IF(LEFT(F54,1)="✔",MIN(IF(H54="",1,H54)+1,5),1))</f>
+        <f t="array" ref="G54">IF(F54="","",IF(I54=TODAY(),"done today",IF(LEFT(F54,1)="✔",MIN(IF(H54="",1,H54)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H54" s="14"/>
@@ -6490,7 +6544,7 @@
         <v/>
       </c>
       <c r="G55" s="9" cm="1" t="str">
-        <f t="array" ref="G55">IF(F55="","",IF(LEFT(F55,1)="✔",MIN(IF(H55="",1,H55)+1,5),1))</f>
+        <f t="array" ref="G55">IF(F55="","",IF(I55=TODAY(),"done today",IF(LEFT(F55,1)="✔",MIN(IF(H55="",1,H55)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H55" s="14"/>
@@ -6523,7 +6577,7 @@
         <v/>
       </c>
       <c r="G56" s="9" cm="1" t="str">
-        <f t="array" ref="G56">IF(F56="","",IF(LEFT(F56,1)="✔",MIN(IF(H56="",1,H56)+1,5),1))</f>
+        <f t="array" ref="G56">IF(F56="","",IF(I56=TODAY(),"done today",IF(LEFT(F56,1)="✔",MIN(IF(H56="",1,H56)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H56" s="14"/>
@@ -6556,7 +6610,7 @@
         <v/>
       </c>
       <c r="G57" s="9" cm="1" t="str">
-        <f t="array" ref="G57">IF(F57="","",IF(LEFT(F57,1)="✔",MIN(IF(H57="",1,H57)+1,5),1))</f>
+        <f t="array" ref="G57">IF(F57="","",IF(I57=TODAY(),"done today",IF(LEFT(F57,1)="✔",MIN(IF(H57="",1,H57)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H57" s="14"/>
@@ -6589,7 +6643,7 @@
         <v/>
       </c>
       <c r="G58" s="9" cm="1" t="str">
-        <f t="array" ref="G58">IF(F58="","",IF(LEFT(F58,1)="✔",MIN(IF(H58="",1,H58)+1,5),1))</f>
+        <f t="array" ref="G58">IF(F58="","",IF(I58=TODAY(),"done today",IF(LEFT(F58,1)="✔",MIN(IF(H58="",1,H58)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H58" s="14"/>
@@ -6622,7 +6676,7 @@
         <v/>
       </c>
       <c r="G59" s="9" cm="1" t="str">
-        <f t="array" ref="G59">IF(F59="","",IF(LEFT(F59,1)="✔",MIN(IF(H59="",1,H59)+1,5),1))</f>
+        <f t="array" ref="G59">IF(F59="","",IF(I59=TODAY(),"done today",IF(LEFT(F59,1)="✔",MIN(IF(H59="",1,H59)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H59" s="14"/>
@@ -6655,7 +6709,7 @@
         <v/>
       </c>
       <c r="G60" s="9" cm="1" t="str">
-        <f t="array" ref="G60">IF(F60="","",IF(LEFT(F60,1)="✔",MIN(IF(H60="",1,H60)+1,5),1))</f>
+        <f t="array" ref="G60">IF(F60="","",IF(I60=TODAY(),"done today",IF(LEFT(F60,1)="✔",MIN(IF(H60="",1,H60)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H60" s="14"/>
@@ -6688,7 +6742,7 @@
         <v/>
       </c>
       <c r="G61" s="9" cm="1" t="str">
-        <f t="array" ref="G61">IF(F61="","",IF(LEFT(F61,1)="✔",MIN(IF(H61="",1,H61)+1,5),1))</f>
+        <f t="array" ref="G61">IF(F61="","",IF(I61=TODAY(),"done today",IF(LEFT(F61,1)="✔",MIN(IF(H61="",1,H61)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H61" s="14"/>
@@ -6713,15 +6767,15 @@
         <v>339</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="13" cm="1" t="str">
-        <f t="array" ref="F62">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$62,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$59:$H$59),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="F62">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$62,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$59:$K$59),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="G62" s="9" cm="1" t="str">
-        <f t="array" ref="G62">IF(F62="","",IF(LEFT(F62,1)="✔",MIN(IF(H62="",1,H62)+1,5),1))</f>
+        <f t="array" ref="G62">IF(F62="","",IF(I62=TODAY(),"done today",IF(LEFT(F62,1)="✔",MIN(IF(H62="",1,H62)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H62" s="14"/>
@@ -6743,10 +6797,10 @@
         <v>247</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="13" cm="1" t="str">
@@ -6754,7 +6808,7 @@
         <v/>
       </c>
       <c r="G63" s="9" cm="1" t="str">
-        <f t="array" ref="G63">IF(F63="","",IF(LEFT(F63,1)="✔",MIN(IF(H63="",1,H63)+1,5),1))</f>
+        <f t="array" ref="G63">IF(F63="","",IF(I63=TODAY(),"done today",IF(LEFT(F63,1)="✔",MIN(IF(H63="",1,H63)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H63" s="14"/>
@@ -6776,10 +6830,10 @@
         <v>247</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="13" cm="1" t="str">
@@ -6787,7 +6841,7 @@
         <v/>
       </c>
       <c r="G64" s="9" cm="1" t="str">
-        <f t="array" ref="G64">IF(F64="","",IF(LEFT(F64,1)="✔",MIN(IF(H64="",1,H64)+1,5),1))</f>
+        <f t="array" ref="G64">IF(F64="","",IF(I64=TODAY(),"done today",IF(LEFT(F64,1)="✔",MIN(IF(H64="",1,H64)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H64" s="14"/>
@@ -6809,10 +6863,10 @@
         <v>247</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="13" cm="1" t="str">
@@ -6820,7 +6874,7 @@
         <v/>
       </c>
       <c r="G65" s="9" cm="1" t="str">
-        <f t="array" ref="G65">IF(F65="","",IF(LEFT(F65,1)="✔",MIN(IF(H65="",1,H65)+1,5),1))</f>
+        <f t="array" ref="G65">IF(F65="","",IF(I65=TODAY(),"done today",IF(LEFT(F65,1)="✔",MIN(IF(H65="",1,H65)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H65" s="14"/>
@@ -6842,10 +6896,10 @@
         <v>247</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="13" cm="1" t="str">
@@ -6853,7 +6907,7 @@
         <v/>
       </c>
       <c r="G66" s="9" cm="1" t="str">
-        <f t="array" ref="G66">IF(F66="","",IF(LEFT(F66,1)="✔",MIN(IF(H66="",1,H66)+1,5),1))</f>
+        <f t="array" ref="G66">IF(F66="","",IF(I66=TODAY(),"done today",IF(LEFT(F66,1)="✔",MIN(IF(H66="",1,H66)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H66" s="14"/>
@@ -6875,10 +6929,10 @@
         <v>247</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="13" cm="1" t="str">
@@ -6886,7 +6940,7 @@
         <v/>
       </c>
       <c r="G67" s="9" cm="1" t="str">
-        <f t="array" ref="G67">IF(F67="","",IF(LEFT(F67,1)="✔",MIN(IF(H67="",1,H67)+1,5),1))</f>
+        <f t="array" ref="G67">IF(F67="","",IF(I67=TODAY(),"done today",IF(LEFT(F67,1)="✔",MIN(IF(H67="",1,H67)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H67" s="14"/>
@@ -6908,10 +6962,10 @@
         <v>247</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="13" cm="1" t="str">
@@ -6919,7 +6973,7 @@
         <v/>
       </c>
       <c r="G68" s="9" cm="1" t="str">
-        <f t="array" ref="G68">IF(F68="","",IF(LEFT(F68,1)="✔",MIN(IF(H68="",1,H68)+1,5),1))</f>
+        <f t="array" ref="G68">IF(F68="","",IF(I68=TODAY(),"done today",IF(LEFT(F68,1)="✔",MIN(IF(H68="",1,H68)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H68" s="14"/>
@@ -6941,10 +6995,10 @@
         <v>247</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="13" cm="1" t="str">
@@ -6952,7 +7006,7 @@
         <v/>
       </c>
       <c r="G69" s="9" cm="1" t="str">
-        <f t="array" ref="G69">IF(F69="","",IF(LEFT(F69,1)="✔",MIN(IF(H69="",1,H69)+1,5),1))</f>
+        <f t="array" ref="G69">IF(F69="","",IF(I69=TODAY(),"done today",IF(LEFT(F69,1)="✔",MIN(IF(H69="",1,H69)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H69" s="14"/>
@@ -6974,10 +7028,10 @@
         <v>247</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="13" cm="1" t="str">
@@ -6985,7 +7039,7 @@
         <v/>
       </c>
       <c r="G70" s="9" cm="1" t="str">
-        <f t="array" ref="G70">IF(F70="","",IF(LEFT(F70,1)="✔",MIN(IF(H70="",1,H70)+1,5),1))</f>
+        <f t="array" ref="G70">IF(F70="","",IF(I70=TODAY(),"done today",IF(LEFT(F70,1)="✔",MIN(IF(H70="",1,H70)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H70" s="14"/>
@@ -7007,18 +7061,18 @@
         <v>247</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="13" cm="1" t="str">
-        <f t="array" ref="F71">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$71,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$68:$E$68),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="F71">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$71,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$68:$J$68),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="G71" s="9" cm="1" t="str">
-        <f t="array" ref="G71">IF(F71="","",IF(LEFT(F71,1)="✔",MIN(IF(H71="",1,H71)+1,5),1))</f>
+        <f t="array" ref="G71">IF(F71="","",IF(I71=TODAY(),"done today",IF(LEFT(F71,1)="✔",MIN(IF(H71="",1,H71)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H71" s="14"/>
@@ -7040,10 +7094,10 @@
         <v>247</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="13" cm="1" t="str">
@@ -7051,7 +7105,7 @@
         <v/>
       </c>
       <c r="G72" s="9" cm="1" t="str">
-        <f t="array" ref="G72">IF(F72="","",IF(LEFT(F72,1)="✔",MIN(IF(H72="",1,H72)+1,5),1))</f>
+        <f t="array" ref="G72">IF(F72="","",IF(I72=TODAY(),"done today",IF(LEFT(F72,1)="✔",MIN(IF(H72="",1,H72)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H72" s="14"/>
@@ -7073,10 +7127,10 @@
         <v>247</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="13" cm="1" t="str">
@@ -7084,7 +7138,7 @@
         <v/>
       </c>
       <c r="G73" s="9" cm="1" t="str">
-        <f t="array" ref="G73">IF(F73="","",IF(LEFT(F73,1)="✔",MIN(IF(H73="",1,H73)+1,5),1))</f>
+        <f t="array" ref="G73">IF(F73="","",IF(I73=TODAY(),"done today",IF(LEFT(F73,1)="✔",MIN(IF(H73="",1,H73)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H73" s="14"/>
@@ -7106,10 +7160,10 @@
         <v>247</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="13" cm="1" t="str">
@@ -7117,7 +7171,7 @@
         <v/>
       </c>
       <c r="G74" s="9" cm="1" t="str">
-        <f t="array" ref="G74">IF(F74="","",IF(LEFT(F74,1)="✔",MIN(IF(H74="",1,H74)+1,5),1))</f>
+        <f t="array" ref="G74">IF(F74="","",IF(I74=TODAY(),"done today",IF(LEFT(F74,1)="✔",MIN(IF(H74="",1,H74)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H74" s="14"/>
@@ -7139,10 +7193,10 @@
         <v>247</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E75" s="12"/>
       <c r="F75" s="13" cm="1" t="str">
@@ -7150,7 +7204,7 @@
         <v/>
       </c>
       <c r="G75" s="9" cm="1" t="str">
-        <f t="array" ref="G75">IF(F75="","",IF(LEFT(F75,1)="✔",MIN(IF(H75="",1,H75)+1,5),1))</f>
+        <f t="array" ref="G75">IF(F75="","",IF(I75=TODAY(),"done today",IF(LEFT(F75,1)="✔",MIN(IF(H75="",1,H75)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H75" s="14"/>
@@ -7169,13 +7223,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="13" cm="1" t="str">
@@ -7183,7 +7237,7 @@
         <v/>
       </c>
       <c r="G76" s="9" cm="1" t="str">
-        <f t="array" ref="G76">IF(F76="","",IF(LEFT(F76,1)="✔",MIN(IF(H76="",1,H76)+1,5),1))</f>
+        <f t="array" ref="G76">IF(F76="","",IF(I76=TODAY(),"done today",IF(LEFT(F76,1)="✔",MIN(IF(H76="",1,H76)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H76" s="14"/>
@@ -7202,13 +7256,13 @@
         <v>73</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="13" cm="1" t="str">
@@ -7216,7 +7270,7 @@
         <v/>
       </c>
       <c r="G77" s="9" cm="1" t="str">
-        <f t="array" ref="G77">IF(F77="","",IF(LEFT(F77,1)="✔",MIN(IF(H77="",1,H77)+1,5),1))</f>
+        <f t="array" ref="G77">IF(F77="","",IF(I77=TODAY(),"done today",IF(LEFT(F77,1)="✔",MIN(IF(H77="",1,H77)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H77" s="14"/>
@@ -7235,13 +7289,13 @@
         <v>74</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="13" cm="1" t="str">
@@ -7249,7 +7303,7 @@
         <v/>
       </c>
       <c r="G78" s="9" cm="1" t="str">
-        <f t="array" ref="G78">IF(F78="","",IF(LEFT(F78,1)="✔",MIN(IF(H78="",1,H78)+1,5),1))</f>
+        <f t="array" ref="G78">IF(F78="","",IF(I78=TODAY(),"done today",IF(LEFT(F78,1)="✔",MIN(IF(H78="",1,H78)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H78" s="14"/>
@@ -7268,13 +7322,13 @@
         <v>75</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="13" cm="1" t="str">
@@ -7282,7 +7336,7 @@
         <v/>
       </c>
       <c r="G79" s="9" cm="1" t="str">
-        <f t="array" ref="G79">IF(F79="","",IF(LEFT(F79,1)="✔",MIN(IF(H79="",1,H79)+1,5),1))</f>
+        <f t="array" ref="G79">IF(F79="","",IF(I79=TODAY(),"done today",IF(LEFT(F79,1)="✔",MIN(IF(H79="",1,H79)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H79" s="14"/>
@@ -7301,13 +7355,13 @@
         <v>76</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="E80" s="12"/>
       <c r="F80" s="13" cm="1" t="str">
@@ -7315,7 +7369,7 @@
         <v/>
       </c>
       <c r="G80" s="9" cm="1" t="str">
-        <f t="array" ref="G80">IF(F80="","",IF(LEFT(F80,1)="✔",MIN(IF(H80="",1,H80)+1,5),1))</f>
+        <f t="array" ref="G80">IF(F80="","",IF(I80=TODAY(),"done today",IF(LEFT(F80,1)="✔",MIN(IF(H80="",1,H80)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H80" s="14"/>
@@ -7334,13 +7388,13 @@
         <v>77</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="13" cm="1" t="str">
@@ -7348,7 +7402,7 @@
         <v/>
       </c>
       <c r="G81" s="9" cm="1" t="str">
-        <f t="array" ref="G81">IF(F81="","",IF(LEFT(F81,1)="✔",MIN(IF(H81="",1,H81)+1,5),1))</f>
+        <f t="array" ref="G81">IF(F81="","",IF(I81=TODAY(),"done today",IF(LEFT(F81,1)="✔",MIN(IF(H81="",1,H81)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H81" s="14"/>
@@ -7367,13 +7421,13 @@
         <v>78</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="13" cm="1" t="str">
@@ -7381,7 +7435,7 @@
         <v/>
       </c>
       <c r="G82" s="9" cm="1" t="str">
-        <f t="array" ref="G82">IF(F82="","",IF(LEFT(F82,1)="✔",MIN(IF(H82="",1,H82)+1,5),1))</f>
+        <f t="array" ref="G82">IF(F82="","",IF(I82=TODAY(),"done today",IF(LEFT(F82,1)="✔",MIN(IF(H82="",1,H82)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H82" s="14"/>
@@ -7400,13 +7454,13 @@
         <v>79</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="13" cm="1" t="str">
@@ -7414,7 +7468,7 @@
         <v/>
       </c>
       <c r="G83" s="9" cm="1" t="str">
-        <f t="array" ref="G83">IF(F83="","",IF(LEFT(F83,1)="✔",MIN(IF(H83="",1,H83)+1,5),1))</f>
+        <f t="array" ref="G83">IF(F83="","",IF(I83=TODAY(),"done today",IF(LEFT(F83,1)="✔",MIN(IF(H83="",1,H83)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H83" s="14"/>
@@ -7433,13 +7487,13 @@
         <v>80</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="13" cm="1" t="str">
@@ -7447,7 +7501,7 @@
         <v/>
       </c>
       <c r="G84" s="9" cm="1" t="str">
-        <f t="array" ref="G84">IF(F84="","",IF(LEFT(F84,1)="✔",MIN(IF(H84="",1,H84)+1,5),1))</f>
+        <f t="array" ref="G84">IF(F84="","",IF(I84=TODAY(),"done today",IF(LEFT(F84,1)="✔",MIN(IF(H84="",1,H84)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H84" s="14"/>
@@ -7466,13 +7520,13 @@
         <v>81</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="E85" s="12"/>
       <c r="F85" s="13" cm="1" t="str">
@@ -7480,7 +7534,7 @@
         <v/>
       </c>
       <c r="G85" s="9" cm="1" t="str">
-        <f t="array" ref="G85">IF(F85="","",IF(LEFT(F85,1)="✔",MIN(IF(H85="",1,H85)+1,5),1))</f>
+        <f t="array" ref="G85">IF(F85="","",IF(I85=TODAY(),"done today",IF(LEFT(F85,1)="✔",MIN(IF(H85="",1,H85)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H85" s="14"/>
@@ -7499,13 +7553,13 @@
         <v>82</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="13" cm="1" t="str">
@@ -7513,7 +7567,7 @@
         <v/>
       </c>
       <c r="G86" s="9" cm="1" t="str">
-        <f t="array" ref="G86">IF(F86="","",IF(LEFT(F86,1)="✔",MIN(IF(H86="",1,H86)+1,5),1))</f>
+        <f t="array" ref="G86">IF(F86="","",IF(I86=TODAY(),"done today",IF(LEFT(F86,1)="✔",MIN(IF(H86="",1,H86)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H86" s="14"/>
@@ -7532,13 +7586,13 @@
         <v>83</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="13" cm="1" t="str">
@@ -7546,7 +7600,7 @@
         <v/>
       </c>
       <c r="G87" s="9" cm="1" t="str">
-        <f t="array" ref="G87">IF(F87="","",IF(LEFT(F87,1)="✔",MIN(IF(H87="",1,H87)+1,5),1))</f>
+        <f t="array" ref="G87">IF(F87="","",IF(I87=TODAY(),"done today",IF(LEFT(F87,1)="✔",MIN(IF(H87="",1,H87)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H87" s="14"/>
@@ -7565,13 +7619,13 @@
         <v>84</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="13" cm="1" t="str">
@@ -7579,7 +7633,7 @@
         <v/>
       </c>
       <c r="G88" s="9" cm="1" t="str">
-        <f t="array" ref="G88">IF(F88="","",IF(LEFT(F88,1)="✔",MIN(IF(H88="",1,H88)+1,5),1))</f>
+        <f t="array" ref="G88">IF(F88="","",IF(I88=TODAY(),"done today",IF(LEFT(F88,1)="✔",MIN(IF(H88="",1,H88)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H88" s="14"/>
@@ -7598,13 +7652,13 @@
         <v>85</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="13" cm="1" t="str">
@@ -7612,7 +7666,7 @@
         <v/>
       </c>
       <c r="G89" s="9" cm="1" t="str">
-        <f t="array" ref="G89">IF(F89="","",IF(LEFT(F89,1)="✔",MIN(IF(H89="",1,H89)+1,5),1))</f>
+        <f t="array" ref="G89">IF(F89="","",IF(I89=TODAY(),"done today",IF(LEFT(F89,1)="✔",MIN(IF(H89="",1,H89)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H89" s="14"/>
@@ -7631,13 +7685,13 @@
         <v>86</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="13" cm="1" t="str">
@@ -7645,7 +7699,7 @@
         <v/>
       </c>
       <c r="G90" s="9" cm="1" t="str">
-        <f t="array" ref="G90">IF(F90="","",IF(LEFT(F90,1)="✔",MIN(IF(H90="",1,H90)+1,5),1))</f>
+        <f t="array" ref="G90">IF(F90="","",IF(I90=TODAY(),"done today",IF(LEFT(F90,1)="✔",MIN(IF(H90="",1,H90)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H90" s="14"/>
@@ -7664,13 +7718,13 @@
         <v>87</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="E91" s="12"/>
       <c r="F91" s="13" cm="1" t="str">
@@ -7678,7 +7732,7 @@
         <v/>
       </c>
       <c r="G91" s="9" cm="1" t="str">
-        <f t="array" ref="G91">IF(F91="","",IF(LEFT(F91,1)="✔",MIN(IF(H91="",1,H91)+1,5),1))</f>
+        <f t="array" ref="G91">IF(F91="","",IF(I91=TODAY(),"done today",IF(LEFT(F91,1)="✔",MIN(IF(H91="",1,H91)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H91" s="14"/>
@@ -7697,13 +7751,13 @@
         <v>88</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="13" cm="1" t="str">
@@ -7711,7 +7765,7 @@
         <v/>
       </c>
       <c r="G92" s="9" cm="1" t="str">
-        <f t="array" ref="G92">IF(F92="","",IF(LEFT(F92,1)="✔",MIN(IF(H92="",1,H92)+1,5),1))</f>
+        <f t="array" ref="G92">IF(F92="","",IF(I92=TODAY(),"done today",IF(LEFT(F92,1)="✔",MIN(IF(H92="",1,H92)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H92" s="14"/>
@@ -7730,13 +7784,13 @@
         <v>89</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="13" cm="1" t="str">
@@ -7744,7 +7798,7 @@
         <v/>
       </c>
       <c r="G93" s="9" cm="1" t="str">
-        <f t="array" ref="G93">IF(F93="","",IF(LEFT(F93,1)="✔",MIN(IF(H93="",1,H93)+1,5),1))</f>
+        <f t="array" ref="G93">IF(F93="","",IF(I93=TODAY(),"done today",IF(LEFT(F93,1)="✔",MIN(IF(H93="",1,H93)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H93" s="14"/>
@@ -7763,13 +7817,13 @@
         <v>90</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="13" cm="1" t="str">
@@ -7777,7 +7831,7 @@
         <v/>
       </c>
       <c r="G94" s="9" cm="1" t="str">
-        <f t="array" ref="G94">IF(F94="","",IF(LEFT(F94,1)="✔",MIN(IF(H94="",1,H94)+1,5),1))</f>
+        <f t="array" ref="G94">IF(F94="","",IF(I94=TODAY(),"done today",IF(LEFT(F94,1)="✔",MIN(IF(H94="",1,H94)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H94" s="14"/>
@@ -7796,13 +7850,13 @@
         <v>91</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="E95" s="12"/>
       <c r="F95" s="13" cm="1" t="str">
@@ -7810,7 +7864,7 @@
         <v/>
       </c>
       <c r="G95" s="9" cm="1" t="str">
-        <f t="array" ref="G95">IF(F95="","",IF(LEFT(F95,1)="✔",MIN(IF(H95="",1,H95)+1,5),1))</f>
+        <f t="array" ref="G95">IF(F95="","",IF(I95=TODAY(),"done today",IF(LEFT(F95,1)="✔",MIN(IF(H95="",1,H95)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H95" s="14"/>
@@ -7829,13 +7883,13 @@
         <v>92</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="E96" s="12"/>
       <c r="F96" s="13" cm="1" t="str">
@@ -7843,7 +7897,7 @@
         <v/>
       </c>
       <c r="G96" s="9" cm="1" t="str">
-        <f t="array" ref="G96">IF(F96="","",IF(LEFT(F96,1)="✔",MIN(IF(H96="",1,H96)+1,5),1))</f>
+        <f t="array" ref="G96">IF(F96="","",IF(I96=TODAY(),"done today",IF(LEFT(F96,1)="✔",MIN(IF(H96="",1,H96)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H96" s="14"/>
@@ -7862,13 +7916,13 @@
         <v>93</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="13" cm="1" t="str">
@@ -7876,7 +7930,7 @@
         <v/>
       </c>
       <c r="G97" s="9" cm="1" t="str">
-        <f t="array" ref="G97">IF(F97="","",IF(LEFT(F97,1)="✔",MIN(IF(H97="",1,H97)+1,5),1))</f>
+        <f t="array" ref="G97">IF(F97="","",IF(I97=TODAY(),"done today",IF(LEFT(F97,1)="✔",MIN(IF(H97="",1,H97)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H97" s="14"/>
@@ -7895,13 +7949,13 @@
         <v>94</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="13" cm="1" t="str">
@@ -7909,7 +7963,7 @@
         <v/>
       </c>
       <c r="G98" s="9" cm="1" t="str">
-        <f t="array" ref="G98">IF(F98="","",IF(LEFT(F98,1)="✔",MIN(IF(H98="",1,H98)+1,5),1))</f>
+        <f t="array" ref="G98">IF(F98="","",IF(I98=TODAY(),"done today",IF(LEFT(F98,1)="✔",MIN(IF(H98="",1,H98)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H98" s="14"/>
@@ -7928,13 +7982,13 @@
         <v>95</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="13" cm="1" t="str">
@@ -7942,7 +7996,7 @@
         <v/>
       </c>
       <c r="G99" s="9" cm="1" t="str">
-        <f t="array" ref="G99">IF(F99="","",IF(LEFT(F99,1)="✔",MIN(IF(H99="",1,H99)+1,5),1))</f>
+        <f t="array" ref="G99">IF(F99="","",IF(I99=TODAY(),"done today",IF(LEFT(F99,1)="✔",MIN(IF(H99="",1,H99)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H99" s="14"/>
@@ -7961,13 +8015,13 @@
         <v>96</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="13" cm="1" t="str">
@@ -7975,7 +8029,7 @@
         <v/>
       </c>
       <c r="G100" s="9" cm="1" t="str">
-        <f t="array" ref="G100">IF(F100="","",IF(LEFT(F100,1)="✔",MIN(IF(H100="",1,H100)+1,5),1))</f>
+        <f t="array" ref="G100">IF(F100="","",IF(I100=TODAY(),"done today",IF(LEFT(F100,1)="✔",MIN(IF(H100="",1,H100)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H100" s="14"/>
@@ -7994,13 +8048,13 @@
         <v>97</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="13" cm="1" t="str">
@@ -8008,7 +8062,7 @@
         <v/>
       </c>
       <c r="G101" s="9" cm="1" t="str">
-        <f t="array" ref="G101">IF(F101="","",IF(LEFT(F101,1)="✔",MIN(IF(H101="",1,H101)+1,5),1))</f>
+        <f t="array" ref="G101">IF(F101="","",IF(I101=TODAY(),"done today",IF(LEFT(F101,1)="✔",MIN(IF(H101="",1,H101)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H101" s="14"/>
@@ -8027,13 +8081,13 @@
         <v>98</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="13" cm="1" t="str">
@@ -8041,7 +8095,7 @@
         <v/>
       </c>
       <c r="G102" s="9" cm="1" t="str">
-        <f t="array" ref="G102">IF(F102="","",IF(LEFT(F102,1)="✔",MIN(IF(H102="",1,H102)+1,5),1))</f>
+        <f t="array" ref="G102">IF(F102="","",IF(I102=TODAY(),"done today",IF(LEFT(F102,1)="✔",MIN(IF(H102="",1,H102)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H102" s="14"/>
@@ -8060,13 +8114,13 @@
         <v>99</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="13" cm="1" t="str">
@@ -8074,7 +8128,7 @@
         <v/>
       </c>
       <c r="G103" s="9" cm="1" t="str">
-        <f t="array" ref="G103">IF(F103="","",IF(LEFT(F103,1)="✔",MIN(IF(H103="",1,H103)+1,5),1))</f>
+        <f t="array" ref="G103">IF(F103="","",IF(I103=TODAY(),"done today",IF(LEFT(F103,1)="✔",MIN(IF(H103="",1,H103)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H103" s="14"/>
@@ -8093,13 +8147,13 @@
         <v>100</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="13" cm="1" t="str">
@@ -8107,7 +8161,7 @@
         <v/>
       </c>
       <c r="G104" s="9" cm="1" t="str">
-        <f t="array" ref="G104">IF(F104="","",IF(LEFT(F104,1)="✔",MIN(IF(H104="",1,H104)+1,5),1))</f>
+        <f t="array" ref="G104">IF(F104="","",IF(I104=TODAY(),"done today",IF(LEFT(F104,1)="✔",MIN(IF(H104="",1,H104)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H104" s="14"/>
@@ -8126,13 +8180,13 @@
         <v>101</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="13" cm="1" t="str">
@@ -8140,7 +8194,7 @@
         <v/>
       </c>
       <c r="G105" s="9" cm="1" t="str">
-        <f t="array" ref="G105">IF(F105="","",IF(LEFT(F105,1)="✔",MIN(IF(H105="",1,H105)+1,5),1))</f>
+        <f t="array" ref="G105">IF(F105="","",IF(I105=TODAY(),"done today",IF(LEFT(F105,1)="✔",MIN(IF(H105="",1,H105)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H105" s="14"/>
@@ -8159,13 +8213,13 @@
         <v>102</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="13" cm="1" t="str">
@@ -8173,7 +8227,7 @@
         <v/>
       </c>
       <c r="G106" s="9" cm="1" t="str">
-        <f t="array" ref="G106">IF(F106="","",IF(LEFT(F106,1)="✔",MIN(IF(H106="",1,H106)+1,5),1))</f>
+        <f t="array" ref="G106">IF(F106="","",IF(I106=TODAY(),"done today",IF(LEFT(F106,1)="✔",MIN(IF(H106="",1,H106)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H106" s="14"/>
@@ -8192,13 +8246,13 @@
         <v>103</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="13" cm="1" t="str">
@@ -8206,7 +8260,7 @@
         <v/>
       </c>
       <c r="G107" s="9" cm="1" t="str">
-        <f t="array" ref="G107">IF(F107="","",IF(LEFT(F107,1)="✔",MIN(IF(H107="",1,H107)+1,5),1))</f>
+        <f t="array" ref="G107">IF(F107="","",IF(I107=TODAY(),"done today",IF(LEFT(F107,1)="✔",MIN(IF(H107="",1,H107)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H107" s="14"/>
@@ -8225,13 +8279,13 @@
         <v>104</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="13" cm="1" t="str">
@@ -8239,7 +8293,7 @@
         <v/>
       </c>
       <c r="G108" s="9" cm="1" t="str">
-        <f t="array" ref="G108">IF(F108="","",IF(LEFT(F108,1)="✔",MIN(IF(H108="",1,H108)+1,5),1))</f>
+        <f t="array" ref="G108">IF(F108="","",IF(I108=TODAY(),"done today",IF(LEFT(F108,1)="✔",MIN(IF(H108="",1,H108)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H108" s="14"/>
@@ -8258,13 +8312,13 @@
         <v>105</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="13" cm="1" t="str">
@@ -8272,7 +8326,7 @@
         <v/>
       </c>
       <c r="G109" s="9" cm="1" t="str">
-        <f t="array" ref="G109">IF(F109="","",IF(LEFT(F109,1)="✔",MIN(IF(H109="",1,H109)+1,5),1))</f>
+        <f t="array" ref="G109">IF(F109="","",IF(I109=TODAY(),"done today",IF(LEFT(F109,1)="✔",MIN(IF(H109="",1,H109)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H109" s="14"/>
@@ -8291,13 +8345,13 @@
         <v>106</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="13" cm="1" t="str">
@@ -8305,7 +8359,7 @@
         <v/>
       </c>
       <c r="G110" s="9" cm="1" t="str">
-        <f t="array" ref="G110">IF(F110="","",IF(LEFT(F110,1)="✔",MIN(IF(H110="",1,H110)+1,5),1))</f>
+        <f t="array" ref="G110">IF(F110="","",IF(I110=TODAY(),"done today",IF(LEFT(F110,1)="✔",MIN(IF(H110="",1,H110)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H110" s="14"/>
@@ -8324,13 +8378,13 @@
         <v>107</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="13" cm="1" t="str">
@@ -8338,7 +8392,7 @@
         <v/>
       </c>
       <c r="G111" s="9" cm="1" t="str">
-        <f t="array" ref="G111">IF(F111="","",IF(LEFT(F111,1)="✔",MIN(IF(H111="",1,H111)+1,5),1))</f>
+        <f t="array" ref="G111">IF(F111="","",IF(I111=TODAY(),"done today",IF(LEFT(F111,1)="✔",MIN(IF(H111="",1,H111)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H111" s="14"/>
@@ -8357,13 +8411,13 @@
         <v>108</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="E112" s="12"/>
       <c r="F112" s="13" cm="1" t="str">
@@ -8371,7 +8425,7 @@
         <v/>
       </c>
       <c r="G112" s="9" cm="1" t="str">
-        <f t="array" ref="G112">IF(F112="","",IF(LEFT(F112,1)="✔",MIN(IF(H112="",1,H112)+1,5),1))</f>
+        <f t="array" ref="G112">IF(F112="","",IF(I112=TODAY(),"done today",IF(LEFT(F112,1)="✔",MIN(IF(H112="",1,H112)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H112" s="14"/>
@@ -8390,13 +8444,13 @@
         <v>109</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="13" cm="1" t="str">
@@ -8404,7 +8458,7 @@
         <v/>
       </c>
       <c r="G113" s="9" cm="1" t="str">
-        <f t="array" ref="G113">IF(F113="","",IF(LEFT(F113,1)="✔",MIN(IF(H113="",1,H113)+1,5),1))</f>
+        <f t="array" ref="G113">IF(F113="","",IF(I113=TODAY(),"done today",IF(LEFT(F113,1)="✔",MIN(IF(H113="",1,H113)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H113" s="14"/>
@@ -8423,13 +8477,13 @@
         <v>110</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="13" cm="1" t="str">
@@ -8437,7 +8491,7 @@
         <v/>
       </c>
       <c r="G114" s="9" cm="1" t="str">
-        <f t="array" ref="G114">IF(F114="","",IF(LEFT(F114,1)="✔",MIN(IF(H114="",1,H114)+1,5),1))</f>
+        <f t="array" ref="G114">IF(F114="","",IF(I114=TODAY(),"done today",IF(LEFT(F114,1)="✔",MIN(IF(H114="",1,H114)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H114" s="14"/>
@@ -8456,13 +8510,13 @@
         <v>111</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="E115" s="12"/>
       <c r="F115" s="13" cm="1" t="str">
@@ -8470,7 +8524,7 @@
         <v/>
       </c>
       <c r="G115" s="9" cm="1" t="str">
-        <f t="array" ref="G115">IF(F115="","",IF(LEFT(F115,1)="✔",MIN(IF(H115="",1,H115)+1,5),1))</f>
+        <f t="array" ref="G115">IF(F115="","",IF(I115=TODAY(),"done today",IF(LEFT(F115,1)="✔",MIN(IF(H115="",1,H115)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H115" s="14"/>
@@ -8489,13 +8543,13 @@
         <v>112</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="E116" s="12"/>
       <c r="F116" s="13" cm="1" t="str">
@@ -8503,7 +8557,7 @@
         <v/>
       </c>
       <c r="G116" s="9" cm="1" t="str">
-        <f t="array" ref="G116">IF(F116="","",IF(LEFT(F116,1)="✔",MIN(IF(H116="",1,H116)+1,5),1))</f>
+        <f t="array" ref="G116">IF(F116="","",IF(I116=TODAY(),"done today",IF(LEFT(F116,1)="✔",MIN(IF(H116="",1,H116)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H116" s="14"/>
@@ -8522,13 +8576,13 @@
         <v>113</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="13" cm="1" t="str">
@@ -8536,7 +8590,7 @@
         <v/>
       </c>
       <c r="G117" s="9" cm="1" t="str">
-        <f t="array" ref="G117">IF(F117="","",IF(LEFT(F117,1)="✔",MIN(IF(H117="",1,H117)+1,5),1))</f>
+        <f t="array" ref="G117">IF(F117="","",IF(I117=TODAY(),"done today",IF(LEFT(F117,1)="✔",MIN(IF(H117="",1,H117)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H117" s="14"/>
@@ -8555,13 +8609,13 @@
         <v>114</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="13" cm="1" t="str">
@@ -8569,7 +8623,7 @@
         <v/>
       </c>
       <c r="G118" s="9" cm="1" t="str">
-        <f t="array" ref="G118">IF(F118="","",IF(LEFT(F118,1)="✔",MIN(IF(H118="",1,H118)+1,5),1))</f>
+        <f t="array" ref="G118">IF(F118="","",IF(I118=TODAY(),"done today",IF(LEFT(F118,1)="✔",MIN(IF(H118="",1,H118)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H118" s="14"/>
@@ -8588,13 +8642,13 @@
         <v>115</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="13" cm="1" t="str">
@@ -8602,7 +8656,7 @@
         <v/>
       </c>
       <c r="G119" s="9" cm="1" t="str">
-        <f t="array" ref="G119">IF(F119="","",IF(LEFT(F119,1)="✔",MIN(IF(H119="",1,H119)+1,5),1))</f>
+        <f t="array" ref="G119">IF(F119="","",IF(I119=TODAY(),"done today",IF(LEFT(F119,1)="✔",MIN(IF(H119="",1,H119)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H119" s="14"/>
@@ -8621,13 +8675,13 @@
         <v>116</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="13" cm="1" t="str">
@@ -8635,7 +8689,7 @@
         <v/>
       </c>
       <c r="G120" s="9" cm="1" t="str">
-        <f t="array" ref="G120">IF(F120="","",IF(LEFT(F120,1)="✔",MIN(IF(H120="",1,H120)+1,5),1))</f>
+        <f t="array" ref="G120">IF(F120="","",IF(I120=TODAY(),"done today",IF(LEFT(F120,1)="✔",MIN(IF(H120="",1,H120)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H120" s="14"/>
@@ -8654,13 +8708,13 @@
         <v>117</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="E121" s="12"/>
       <c r="F121" s="13" cm="1" t="str">
@@ -8668,7 +8722,7 @@
         <v/>
       </c>
       <c r="G121" s="9" cm="1" t="str">
-        <f t="array" ref="G121">IF(F121="","",IF(LEFT(F121,1)="✔",MIN(IF(H121="",1,H121)+1,5),1))</f>
+        <f t="array" ref="G121">IF(F121="","",IF(I121=TODAY(),"done today",IF(LEFT(F121,1)="✔",MIN(IF(H121="",1,H121)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H121" s="14"/>
@@ -8687,13 +8741,13 @@
         <v>118</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="E122" s="12"/>
       <c r="F122" s="13" cm="1" t="str">
@@ -8701,7 +8755,7 @@
         <v/>
       </c>
       <c r="G122" s="9" cm="1" t="str">
-        <f t="array" ref="G122">IF(F122="","",IF(LEFT(F122,1)="✔",MIN(IF(H122="",1,H122)+1,5),1))</f>
+        <f t="array" ref="G122">IF(F122="","",IF(I122=TODAY(),"done today",IF(LEFT(F122,1)="✔",MIN(IF(H122="",1,H122)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H122" s="14"/>
@@ -8720,13 +8774,13 @@
         <v>119</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="E123" s="12"/>
       <c r="F123" s="13" cm="1" t="str">
@@ -8734,7 +8788,7 @@
         <v/>
       </c>
       <c r="G123" s="9" cm="1" t="str">
-        <f t="array" ref="G123">IF(F123="","",IF(LEFT(F123,1)="✔",MIN(IF(H123="",1,H123)+1,5),1))</f>
+        <f t="array" ref="G123">IF(F123="","",IF(I123=TODAY(),"done today",IF(LEFT(F123,1)="✔",MIN(IF(H123="",1,H123)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H123" s="14"/>
@@ -8753,13 +8807,13 @@
         <v>120</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="E124" s="12"/>
       <c r="F124" s="13" cm="1" t="str">
@@ -8767,7 +8821,7 @@
         <v/>
       </c>
       <c r="G124" s="9" cm="1" t="str">
-        <f t="array" ref="G124">IF(F124="","",IF(LEFT(F124,1)="✔",MIN(IF(H124="",1,H124)+1,5),1))</f>
+        <f t="array" ref="G124">IF(F124="","",IF(I124=TODAY(),"done today",IF(LEFT(F124,1)="✔",MIN(IF(H124="",1,H124)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H124" s="14"/>
@@ -8789,10 +8843,10 @@
         <v>203</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="E125" s="12"/>
       <c r="F125" s="13" cm="1" t="str">
@@ -8800,7 +8854,7 @@
         <v/>
       </c>
       <c r="G125" s="9" cm="1" t="str">
-        <f t="array" ref="G125">IF(F125="","",IF(LEFT(F125,1)="✔",MIN(IF(H125="",1,H125)+1,5),1))</f>
+        <f t="array" ref="G125">IF(F125="","",IF(I125=TODAY(),"done today",IF(LEFT(F125,1)="✔",MIN(IF(H125="",1,H125)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H125" s="14"/>
@@ -8822,10 +8876,10 @@
         <v>203</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="E126" s="12"/>
       <c r="F126" s="13" cm="1" t="str">
@@ -8833,7 +8887,7 @@
         <v/>
       </c>
       <c r="G126" s="9" cm="1" t="str">
-        <f t="array" ref="G126">IF(F126="","",IF(LEFT(F126,1)="✔",MIN(IF(H126="",1,H126)+1,5),1))</f>
+        <f t="array" ref="G126">IF(F126="","",IF(I126=TODAY(),"done today",IF(LEFT(F126,1)="✔",MIN(IF(H126="",1,H126)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H126" s="14"/>
@@ -8855,10 +8909,10 @@
         <v>203</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="E127" s="12"/>
       <c r="F127" s="13" cm="1" t="str">
@@ -8866,7 +8920,7 @@
         <v/>
       </c>
       <c r="G127" s="9" cm="1" t="str">
-        <f t="array" ref="G127">IF(F127="","",IF(LEFT(F127,1)="✔",MIN(IF(H127="",1,H127)+1,5),1))</f>
+        <f t="array" ref="G127">IF(F127="","",IF(I127=TODAY(),"done today",IF(LEFT(F127,1)="✔",MIN(IF(H127="",1,H127)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H127" s="14"/>
@@ -8888,10 +8942,10 @@
         <v>203</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="E128" s="12"/>
       <c r="F128" s="13" cm="1" t="str">
@@ -8899,7 +8953,7 @@
         <v/>
       </c>
       <c r="G128" s="9" cm="1" t="str">
-        <f t="array" ref="G128">IF(F128="","",IF(LEFT(F128,1)="✔",MIN(IF(H128="",1,H128)+1,5),1))</f>
+        <f t="array" ref="G128">IF(F128="","",IF(I128=TODAY(),"done today",IF(LEFT(F128,1)="✔",MIN(IF(H128="",1,H128)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H128" s="14"/>
@@ -8921,10 +8975,10 @@
         <v>203</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="E129" s="12"/>
       <c r="F129" s="13" cm="1" t="str">
@@ -8932,7 +8986,7 @@
         <v/>
       </c>
       <c r="G129" s="9" cm="1" t="str">
-        <f t="array" ref="G129">IF(F129="","",IF(LEFT(F129,1)="✔",MIN(IF(H129="",1,H129)+1,5),1))</f>
+        <f t="array" ref="G129">IF(F129="","",IF(I129=TODAY(),"done today",IF(LEFT(F129,1)="✔",MIN(IF(H129="",1,H129)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H129" s="14"/>
@@ -8954,18 +9008,18 @@
         <v>203</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>854</v>
+        <v>867</v>
       </c>
       <c r="E130" s="12"/>
       <c r="F130" s="13" cm="1" t="str">
-        <f t="array" ref="F130">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$130,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$127:$F$127),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="F130">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$130,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$127:$K$127),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="G130" s="9" cm="1" t="str">
-        <f t="array" ref="G130">IF(F130="","",IF(LEFT(F130,1)="✔",MIN(IF(H130="",1,H130)+1,5),1))</f>
+        <f t="array" ref="G130">IF(F130="","",IF(I130=TODAY(),"done today",IF(LEFT(F130,1)="✔",MIN(IF(H130="",1,H130)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H130" s="14"/>
@@ -8987,10 +9041,10 @@
         <v>203</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>864</v>
+        <v>877</v>
       </c>
       <c r="E131" s="12"/>
       <c r="F131" s="13" cm="1" t="str">
@@ -8998,7 +9052,7 @@
         <v/>
       </c>
       <c r="G131" s="9" cm="1" t="str">
-        <f t="array" ref="G131">IF(F131="","",IF(LEFT(F131,1)="✔",MIN(IF(H131="",1,H131)+1,5),1))</f>
+        <f t="array" ref="G131">IF(F131="","",IF(I131=TODAY(),"done today",IF(LEFT(F131,1)="✔",MIN(IF(H131="",1,H131)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H131" s="14"/>
@@ -9020,10 +9074,10 @@
         <v>203</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="E132" s="12"/>
       <c r="F132" s="13" cm="1" t="str">
@@ -9031,7 +9085,7 @@
         <v/>
       </c>
       <c r="G132" s="9" cm="1" t="str">
-        <f t="array" ref="G132">IF(F132="","",IF(LEFT(F132,1)="✔",MIN(IF(H132="",1,H132)+1,5),1))</f>
+        <f t="array" ref="G132">IF(F132="","",IF(I132=TODAY(),"done today",IF(LEFT(F132,1)="✔",MIN(IF(H132="",1,H132)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H132" s="14"/>
@@ -9053,18 +9107,18 @@
         <v>203</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="E133" s="12"/>
       <c r="F133" s="13" cm="1" t="str">
-        <f t="array" ref="F133">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$133,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$130:$E$130),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="F133">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$133,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$130:$P$130),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="G133" s="9" cm="1" t="str">
-        <f t="array" ref="G133">IF(F133="","",IF(LEFT(F133,1)="✔",MIN(IF(H133="",1,H133)+1,5),1))</f>
+        <f t="array" ref="G133">IF(F133="","",IF(I133=TODAY(),"done today",IF(LEFT(F133,1)="✔",MIN(IF(H133="",1,H133)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H133" s="14"/>
@@ -9086,10 +9140,10 @@
         <v>203</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="E134" s="12"/>
       <c r="F134" s="13" cm="1" t="str">
@@ -9097,7 +9151,7 @@
         <v/>
       </c>
       <c r="G134" s="9" cm="1" t="str">
-        <f t="array" ref="G134">IF(F134="","",IF(LEFT(F134,1)="✔",MIN(IF(H134="",1,H134)+1,5),1))</f>
+        <f t="array" ref="G134">IF(F134="","",IF(I134=TODAY(),"done today",IF(LEFT(F134,1)="✔",MIN(IF(H134="",1,H134)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H134" s="14"/>
@@ -9119,10 +9173,10 @@
         <v>203</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>890</v>
+        <v>903</v>
       </c>
       <c r="E135" s="12"/>
       <c r="F135" s="13" cm="1" t="str">
@@ -9130,7 +9184,7 @@
         <v/>
       </c>
       <c r="G135" s="9" cm="1" t="str">
-        <f t="array" ref="G135">IF(F135="","",IF(LEFT(F135,1)="✔",MIN(IF(H135="",1,H135)+1,5),1))</f>
+        <f t="array" ref="G135">IF(F135="","",IF(I135=TODAY(),"done today",IF(LEFT(F135,1)="✔",MIN(IF(H135="",1,H135)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H135" s="14"/>
@@ -9152,10 +9206,10 @@
         <v>203</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="E136" s="12"/>
       <c r="F136" s="13" cm="1" t="str">
@@ -9163,7 +9217,7 @@
         <v/>
       </c>
       <c r="G136" s="9" cm="1" t="str">
-        <f t="array" ref="G136">IF(F136="","",IF(LEFT(F136,1)="✔",MIN(IF(H136="",1,H136)+1,5),1))</f>
+        <f t="array" ref="G136">IF(F136="","",IF(I136=TODAY(),"done today",IF(LEFT(F136,1)="✔",MIN(IF(H136="",1,H136)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H136" s="14"/>
@@ -9185,10 +9239,10 @@
         <v>42</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>907</v>
+        <v>920</v>
       </c>
       <c r="E137" s="12"/>
       <c r="F137" s="13" cm="1" t="str">
@@ -9196,7 +9250,7 @@
         <v/>
       </c>
       <c r="G137" s="9" cm="1" t="str">
-        <f t="array" ref="G137">IF(F137="","",IF(LEFT(F137,1)="✔",MIN(IF(H137="",1,H137)+1,5),1))</f>
+        <f t="array" ref="G137">IF(F137="","",IF(I137=TODAY(),"done today",IF(LEFT(F137,1)="✔",MIN(IF(H137="",1,H137)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H137" s="14"/>
@@ -9218,10 +9272,10 @@
         <v>42</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>916</v>
+        <v>929</v>
       </c>
       <c r="E138" s="12"/>
       <c r="F138" s="13" cm="1" t="str">
@@ -9229,7 +9283,7 @@
         <v/>
       </c>
       <c r="G138" s="9" cm="1" t="str">
-        <f t="array" ref="G138">IF(F138="","",IF(LEFT(F138,1)="✔",MIN(IF(H138="",1,H138)+1,5),1))</f>
+        <f t="array" ref="G138">IF(F138="","",IF(I138=TODAY(),"done today",IF(LEFT(F138,1)="✔",MIN(IF(H138="",1,H138)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H138" s="14"/>
@@ -9251,10 +9305,10 @@
         <v>42</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>925</v>
+        <v>938</v>
       </c>
       <c r="E139" s="12"/>
       <c r="F139" s="13" cm="1" t="str">
@@ -9262,7 +9316,7 @@
         <v/>
       </c>
       <c r="G139" s="9" cm="1" t="str">
-        <f t="array" ref="G139">IF(F139="","",IF(LEFT(F139,1)="✔",MIN(IF(H139="",1,H139)+1,5),1))</f>
+        <f t="array" ref="G139">IF(F139="","",IF(I139=TODAY(),"done today",IF(LEFT(F139,1)="✔",MIN(IF(H139="",1,H139)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H139" s="14"/>
@@ -9284,10 +9338,10 @@
         <v>42</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>934</v>
+        <v>947</v>
       </c>
       <c r="E140" s="12"/>
       <c r="F140" s="13" cm="1" t="str">
@@ -9295,7 +9349,7 @@
         <v/>
       </c>
       <c r="G140" s="9" cm="1" t="str">
-        <f t="array" ref="G140">IF(F140="","",IF(LEFT(F140,1)="✔",MIN(IF(H140="",1,H140)+1,5),1))</f>
+        <f t="array" ref="G140">IF(F140="","",IF(I140=TODAY(),"done today",IF(LEFT(F140,1)="✔",MIN(IF(H140="",1,H140)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H140" s="14"/>
@@ -9317,10 +9371,10 @@
         <v>42</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>936</v>
+        <v>949</v>
       </c>
       <c r="E141" s="12"/>
       <c r="F141" s="13" cm="1" t="str">
@@ -9328,7 +9382,7 @@
         <v/>
       </c>
       <c r="G141" s="9" cm="1" t="str">
-        <f t="array" ref="G141">IF(F141="","",IF(LEFT(F141,1)="✔",MIN(IF(H141="",1,H141)+1,5),1))</f>
+        <f t="array" ref="G141">IF(F141="","",IF(I141=TODAY(),"done today",IF(LEFT(F141,1)="✔",MIN(IF(H141="",1,H141)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H141" s="14"/>
@@ -9350,10 +9404,10 @@
         <v>42</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>946</v>
+        <v>959</v>
       </c>
       <c r="E142" s="12"/>
       <c r="F142" s="13" cm="1" t="str">
@@ -9361,7 +9415,7 @@
         <v/>
       </c>
       <c r="G142" s="9" cm="1" t="str">
-        <f t="array" ref="G142">IF(F142="","",IF(LEFT(F142,1)="✔",MIN(IF(H142="",1,H142)+1,5),1))</f>
+        <f t="array" ref="G142">IF(F142="","",IF(I142=TODAY(),"done today",IF(LEFT(F142,1)="✔",MIN(IF(H142="",1,H142)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H142" s="14"/>
@@ -9383,10 +9437,10 @@
         <v>42</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>955</v>
+        <v>968</v>
       </c>
       <c r="E143" s="12"/>
       <c r="F143" s="13" cm="1" t="str">
@@ -9394,7 +9448,7 @@
         <v/>
       </c>
       <c r="G143" s="9" cm="1" t="str">
-        <f t="array" ref="G143">IF(F143="","",IF(LEFT(F143,1)="✔",MIN(IF(H143="",1,H143)+1,5),1))</f>
+        <f t="array" ref="G143">IF(F143="","",IF(I143=TODAY(),"done today",IF(LEFT(F143,1)="✔",MIN(IF(H143="",1,H143)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H143" s="14"/>
@@ -9416,10 +9470,10 @@
         <v>42</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>964</v>
+        <v>977</v>
       </c>
       <c r="E144" s="12"/>
       <c r="F144" s="13" cm="1" t="str">
@@ -9427,7 +9481,7 @@
         <v/>
       </c>
       <c r="G144" s="9" cm="1" t="str">
-        <f t="array" ref="G144">IF(F144="","",IF(LEFT(F144,1)="✔",MIN(IF(H144="",1,H144)+1,5),1))</f>
+        <f t="array" ref="G144">IF(F144="","",IF(I144=TODAY(),"done today",IF(LEFT(F144,1)="✔",MIN(IF(H144="",1,H144)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H144" s="14"/>
@@ -9449,10 +9503,10 @@
         <v>42</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>973</v>
+        <v>986</v>
       </c>
       <c r="E145" s="12"/>
       <c r="F145" s="13" cm="1" t="str">
@@ -9460,7 +9514,7 @@
         <v/>
       </c>
       <c r="G145" s="9" cm="1" t="str">
-        <f t="array" ref="G145">IF(F145="","",IF(LEFT(F145,1)="✔",MIN(IF(H145="",1,H145)+1,5),1))</f>
+        <f t="array" ref="G145">IF(F145="","",IF(I145=TODAY(),"done today",IF(LEFT(F145,1)="✔",MIN(IF(H145="",1,H145)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H145" s="14"/>
@@ -9482,10 +9536,10 @@
         <v>42</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>982</v>
+        <v>995</v>
       </c>
       <c r="E146" s="12"/>
       <c r="F146" s="13" cm="1" t="str">
@@ -9493,7 +9547,7 @@
         <v/>
       </c>
       <c r="G146" s="9" cm="1" t="str">
-        <f t="array" ref="G146">IF(F146="","",IF(LEFT(F146,1)="✔",MIN(IF(H146="",1,H146)+1,5),1))</f>
+        <f t="array" ref="G146">IF(F146="","",IF(I146=TODAY(),"done today",IF(LEFT(F146,1)="✔",MIN(IF(H146="",1,H146)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H146" s="14"/>
@@ -9515,10 +9569,10 @@
         <v>42</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>991</v>
+        <v>1004</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="E147" s="12"/>
       <c r="F147" s="13" cm="1" t="str">
@@ -9526,7 +9580,7 @@
         <v/>
       </c>
       <c r="G147" s="9" cm="1" t="str">
-        <f t="array" ref="G147">IF(F147="","",IF(LEFT(F147,1)="✔",MIN(IF(H147="",1,H147)+1,5),1))</f>
+        <f t="array" ref="G147">IF(F147="","",IF(I147=TODAY(),"done today",IF(LEFT(F147,1)="✔",MIN(IF(H147="",1,H147)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H147" s="14"/>
@@ -9548,10 +9602,10 @@
         <v>42</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>991</v>
+        <v>1004</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>1001</v>
+        <v>1014</v>
       </c>
       <c r="E148" s="12"/>
       <c r="F148" s="13" cm="1" t="str">
@@ -9559,7 +9613,7 @@
         <v/>
       </c>
       <c r="G148" s="9" cm="1" t="str">
-        <f t="array" ref="G148">IF(F148="","",IF(LEFT(F148,1)="✔",MIN(IF(H148="",1,H148)+1,5),1))</f>
+        <f t="array" ref="G148">IF(F148="","",IF(I148=TODAY(),"done today",IF(LEFT(F148,1)="✔",MIN(IF(H148="",1,H148)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H148" s="14"/>
@@ -9581,18 +9635,18 @@
         <v>42</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>991</v>
+        <v>1004</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>1003</v>
+        <v>1016</v>
       </c>
       <c r="E149" s="12"/>
       <c r="F149" s="13" cm="1" t="str">
-        <f t="array" ref="F149">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$149,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$146:$E$146),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="F149">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$149,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$146:$P$146),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="G149" s="9" cm="1" t="str">
-        <f t="array" ref="G149">IF(F149="","",IF(LEFT(F149,1)="✔",MIN(IF(H149="",1,H149)+1,5),1))</f>
+        <f t="array" ref="G149">IF(F149="","",IF(I149=TODAY(),"done today",IF(LEFT(F149,1)="✔",MIN(IF(H149="",1,H149)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H149" s="14"/>
@@ -9614,10 +9668,10 @@
         <v>42</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>1013</v>
+        <v>1026</v>
       </c>
       <c r="E150" s="12"/>
       <c r="F150" s="13" cm="1" t="str">
@@ -9625,7 +9679,7 @@
         <v/>
       </c>
       <c r="G150" s="9" cm="1" t="str">
-        <f t="array" ref="G150">IF(F150="","",IF(LEFT(F150,1)="✔",MIN(IF(H150="",1,H150)+1,5),1))</f>
+        <f t="array" ref="G150">IF(F150="","",IF(I150=TODAY(),"done today",IF(LEFT(F150,1)="✔",MIN(IF(H150="",1,H150)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H150" s="14"/>
@@ -9647,10 +9701,10 @@
         <v>42</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>1022</v>
+        <v>1035</v>
       </c>
       <c r="E151" s="12"/>
       <c r="F151" s="13" cm="1" t="str">
@@ -9658,7 +9712,7 @@
         <v/>
       </c>
       <c r="G151" s="9" cm="1" t="str">
-        <f t="array" ref="G151">IF(F151="","",IF(LEFT(F151,1)="✔",MIN(IF(H151="",1,H151)+1,5),1))</f>
+        <f t="array" ref="G151">IF(F151="","",IF(I151=TODAY(),"done today",IF(LEFT(F151,1)="✔",MIN(IF(H151="",1,H151)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H151" s="14"/>
@@ -9680,10 +9734,10 @@
         <v>42</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="E152" s="12"/>
       <c r="F152" s="13" cm="1" t="str">
@@ -9691,7 +9745,7 @@
         <v/>
       </c>
       <c r="G152" s="9" cm="1" t="str">
-        <f t="array" ref="G152">IF(F152="","",IF(LEFT(F152,1)="✔",MIN(IF(H152="",1,H152)+1,5),1))</f>
+        <f t="array" ref="G152">IF(F152="","",IF(I152=TODAY(),"done today",IF(LEFT(F152,1)="✔",MIN(IF(H152="",1,H152)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H152" s="14"/>
@@ -9710,13 +9764,13 @@
         <v>149</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>1042</v>
+        <v>1055</v>
       </c>
       <c r="E153" s="12"/>
       <c r="F153" s="13" cm="1" t="str">
@@ -9724,7 +9778,7 @@
         <v/>
       </c>
       <c r="G153" s="9" cm="1" t="str">
-        <f t="array" ref="G153">IF(F153="","",IF(LEFT(F153,1)="✔",MIN(IF(H153="",1,H153)+1,5),1))</f>
+        <f t="array" ref="G153">IF(F153="","",IF(I153=TODAY(),"done today",IF(LEFT(F153,1)="✔",MIN(IF(H153="",1,H153)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H153" s="14"/>
@@ -9743,13 +9797,13 @@
         <v>150</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>1050</v>
+        <v>1063</v>
       </c>
       <c r="E154" s="12"/>
       <c r="F154" s="13" cm="1" t="str">
@@ -9757,7 +9811,7 @@
         <v/>
       </c>
       <c r="G154" s="9" cm="1" t="str">
-        <f t="array" ref="G154">IF(F154="","",IF(LEFT(F154,1)="✔",MIN(IF(H154="",1,H154)+1,5),1))</f>
+        <f t="array" ref="G154">IF(F154="","",IF(I154=TODAY(),"done today",IF(LEFT(F154,1)="✔",MIN(IF(H154="",1,H154)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H154" s="14"/>
@@ -9776,13 +9830,13 @@
         <v>151</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>1058</v>
+        <v>1071</v>
       </c>
       <c r="E155" s="12"/>
       <c r="F155" s="13" cm="1" t="str">
@@ -9790,7 +9844,7 @@
         <v/>
       </c>
       <c r="G155" s="9" cm="1" t="str">
-        <f t="array" ref="G155">IF(F155="","",IF(LEFT(F155,1)="✔",MIN(IF(H155="",1,H155)+1,5),1))</f>
+        <f t="array" ref="G155">IF(F155="","",IF(I155=TODAY(),"done today",IF(LEFT(F155,1)="✔",MIN(IF(H155="",1,H155)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H155" s="14"/>
@@ -9809,13 +9863,13 @@
         <v>152</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="E156" s="12"/>
       <c r="F156" s="13" cm="1" t="str">
@@ -9823,7 +9877,7 @@
         <v/>
       </c>
       <c r="G156" s="9" cm="1" t="str">
-        <f t="array" ref="G156">IF(F156="","",IF(LEFT(F156,1)="✔",MIN(IF(H156="",1,H156)+1,5),1))</f>
+        <f t="array" ref="G156">IF(F156="","",IF(I156=TODAY(),"done today",IF(LEFT(F156,1)="✔",MIN(IF(H156="",1,H156)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H156" s="14"/>
@@ -9842,13 +9896,13 @@
         <v>153</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>1074</v>
+        <v>1087</v>
       </c>
       <c r="E157" s="12"/>
       <c r="F157" s="13" cm="1" t="str">
@@ -9856,7 +9910,7 @@
         <v/>
       </c>
       <c r="G157" s="9" cm="1" t="str">
-        <f t="array" ref="G157">IF(F157="","",IF(LEFT(F157,1)="✔",MIN(IF(H157="",1,H157)+1,5),1))</f>
+        <f t="array" ref="G157">IF(F157="","",IF(I157=TODAY(),"done today",IF(LEFT(F157,1)="✔",MIN(IF(H157="",1,H157)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H157" s="14"/>
@@ -9875,13 +9929,13 @@
         <v>154</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="E158" s="12"/>
       <c r="F158" s="13" cm="1" t="str">
@@ -9889,7 +9943,7 @@
         <v/>
       </c>
       <c r="G158" s="9" cm="1" t="str">
-        <f t="array" ref="G158">IF(F158="","",IF(LEFT(F158,1)="✔",MIN(IF(H158="",1,H158)+1,5),1))</f>
+        <f t="array" ref="G158">IF(F158="","",IF(I158=TODAY(),"done today",IF(LEFT(F158,1)="✔",MIN(IF(H158="",1,H158)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H158" s="14"/>
@@ -9908,13 +9962,13 @@
         <v>155</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>1091</v>
+        <v>1104</v>
       </c>
       <c r="E159" s="12"/>
       <c r="F159" s="13" cm="1" t="str">
@@ -9922,7 +9976,7 @@
         <v/>
       </c>
       <c r="G159" s="9" cm="1" t="str">
-        <f t="array" ref="G159">IF(F159="","",IF(LEFT(F159,1)="✔",MIN(IF(H159="",1,H159)+1,5),1))</f>
+        <f t="array" ref="G159">IF(F159="","",IF(I159=TODAY(),"done today",IF(LEFT(F159,1)="✔",MIN(IF(H159="",1,H159)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H159" s="14"/>
@@ -9941,13 +9995,13 @@
         <v>156</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>1097</v>
+        <v>1110</v>
       </c>
       <c r="E160" s="12"/>
       <c r="F160" s="13" cm="1" t="str">
@@ -9955,7 +10009,7 @@
         <v/>
       </c>
       <c r="G160" s="9" cm="1" t="str">
-        <f t="array" ref="G160">IF(F160="","",IF(LEFT(F160,1)="✔",MIN(IF(H160="",1,H160)+1,5),1))</f>
+        <f t="array" ref="G160">IF(F160="","",IF(I160=TODAY(),"done today",IF(LEFT(F160,1)="✔",MIN(IF(H160="",1,H160)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H160" s="14"/>
@@ -9974,13 +10028,13 @@
         <v>157</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>1104</v>
+        <v>1117</v>
       </c>
       <c r="E161" s="12"/>
       <c r="F161" s="13" cm="1" t="str">
@@ -9988,7 +10042,7 @@
         <v/>
       </c>
       <c r="G161" s="9" cm="1" t="str">
-        <f t="array" ref="G161">IF(F161="","",IF(LEFT(F161,1)="✔",MIN(IF(H161="",1,H161)+1,5),1))</f>
+        <f t="array" ref="G161">IF(F161="","",IF(I161=TODAY(),"done today",IF(LEFT(F161,1)="✔",MIN(IF(H161="",1,H161)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H161" s="14"/>
@@ -10007,13 +10061,13 @@
         <v>158</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="E162" s="12"/>
       <c r="F162" s="13" cm="1" t="str">
@@ -10021,7 +10075,7 @@
         <v/>
       </c>
       <c r="G162" s="9" cm="1" t="str">
-        <f t="array" ref="G162">IF(F162="","",IF(LEFT(F162,1)="✔",MIN(IF(H162="",1,H162)+1,5),1))</f>
+        <f t="array" ref="G162">IF(F162="","",IF(I162=TODAY(),"done today",IF(LEFT(F162,1)="✔",MIN(IF(H162="",1,H162)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H162" s="14"/>
@@ -10040,13 +10094,13 @@
         <v>159</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>1123</v>
+        <v>1136</v>
       </c>
       <c r="E163" s="12"/>
       <c r="F163" s="13" cm="1" t="str">
@@ -10054,7 +10108,7 @@
         <v/>
       </c>
       <c r="G163" s="9" cm="1" t="str">
-        <f t="array" ref="G163">IF(F163="","",IF(LEFT(F163,1)="✔",MIN(IF(H163="",1,H163)+1,5),1))</f>
+        <f t="array" ref="G163">IF(F163="","",IF(I163=TODAY(),"done today",IF(LEFT(F163,1)="✔",MIN(IF(H163="",1,H163)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H163" s="14"/>
@@ -10073,13 +10127,13 @@
         <v>160</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="E164" s="12"/>
       <c r="F164" s="13" cm="1" t="str">
@@ -10087,7 +10141,7 @@
         <v/>
       </c>
       <c r="G164" s="9" cm="1" t="str">
-        <f t="array" ref="G164">IF(F164="","",IF(LEFT(F164,1)="✔",MIN(IF(H164="",1,H164)+1,5),1))</f>
+        <f t="array" ref="G164">IF(F164="","",IF(I164=TODAY(),"done today",IF(LEFT(F164,1)="✔",MIN(IF(H164="",1,H164)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H164" s="14"/>
@@ -10106,13 +10160,13 @@
         <v>161</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>1141</v>
+        <v>1154</v>
       </c>
       <c r="E165" s="12"/>
       <c r="F165" s="13" cm="1" t="str">
@@ -10120,7 +10174,7 @@
         <v/>
       </c>
       <c r="G165" s="9" cm="1" t="str">
-        <f t="array" ref="G165">IF(F165="","",IF(LEFT(F165,1)="✔",MIN(IF(H165="",1,H165)+1,5),1))</f>
+        <f t="array" ref="G165">IF(F165="","",IF(I165=TODAY(),"done today",IF(LEFT(F165,1)="✔",MIN(IF(H165="",1,H165)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H165" s="14"/>
@@ -10139,13 +10193,13 @@
         <v>162</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="E166" s="12"/>
       <c r="F166" s="13" cm="1" t="str">
@@ -10153,7 +10207,7 @@
         <v/>
       </c>
       <c r="G166" s="9" cm="1" t="str">
-        <f t="array" ref="G166">IF(F166="","",IF(LEFT(F166,1)="✔",MIN(IF(H166="",1,H166)+1,5),1))</f>
+        <f t="array" ref="G166">IF(F166="","",IF(I166=TODAY(),"done today",IF(LEFT(F166,1)="✔",MIN(IF(H166="",1,H166)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H166" s="14"/>
@@ -10172,13 +10226,13 @@
         <v>163</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>1157</v>
+        <v>1170</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>1158</v>
+        <v>1171</v>
       </c>
       <c r="E167" s="12"/>
       <c r="F167" s="13" cm="1" t="str">
@@ -10186,7 +10240,7 @@
         <v/>
       </c>
       <c r="G167" s="9" cm="1" t="str">
-        <f t="array" ref="G167">IF(F167="","",IF(LEFT(F167,1)="✔",MIN(IF(H167="",1,H167)+1,5),1))</f>
+        <f t="array" ref="G167">IF(F167="","",IF(I167=TODAY(),"done today",IF(LEFT(F167,1)="✔",MIN(IF(H167="",1,H167)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H167" s="14"/>
@@ -10205,21 +10259,21 @@
         <v>164</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>1157</v>
+        <v>1170</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>1163</v>
+        <v>1181</v>
       </c>
       <c r="E168" s="12"/>
       <c r="F168" s="13" cm="1" t="str">
-        <f t="array" ref="F168">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$168,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$165:$G$165),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="F168">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$168,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$165:$L$165),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="G168" s="9" cm="1" t="str">
-        <f t="array" ref="G168">IF(F168="","",IF(LEFT(F168,1)="✔",MIN(IF(H168="",1,H168)+1,5),1))</f>
+        <f t="array" ref="G168">IF(F168="","",IF(I168=TODAY(),"done today",IF(LEFT(F168,1)="✔",MIN(IF(H168="",1,H168)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H168" s="14"/>
@@ -10238,13 +10292,13 @@
         <v>165</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>1157</v>
+        <v>1170</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>1167</v>
+        <v>1185</v>
       </c>
       <c r="E169" s="12"/>
       <c r="F169" s="13" cm="1" t="str">
@@ -10252,7 +10306,7 @@
         <v/>
       </c>
       <c r="G169" s="9" cm="1" t="str">
-        <f t="array" ref="G169">IF(F169="","",IF(LEFT(F169,1)="✔",MIN(IF(H169="",1,H169)+1,5),1))</f>
+        <f t="array" ref="G169">IF(F169="","",IF(I169=TODAY(),"done today",IF(LEFT(F169,1)="✔",MIN(IF(H169="",1,H169)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H169" s="14"/>
@@ -10271,13 +10325,13 @@
         <v>166</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>1157</v>
+        <v>1170</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>1176</v>
+        <v>1194</v>
       </c>
       <c r="E170" s="12"/>
       <c r="F170" s="13" cm="1" t="str">
@@ -10285,7 +10339,7 @@
         <v/>
       </c>
       <c r="G170" s="9" cm="1" t="str">
-        <f t="array" ref="G170">IF(F170="","",IF(LEFT(F170,1)="✔",MIN(IF(H170="",1,H170)+1,5),1))</f>
+        <f t="array" ref="G170">IF(F170="","",IF(I170=TODAY(),"done today",IF(LEFT(F170,1)="✔",MIN(IF(H170="",1,H170)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H170" s="14"/>
@@ -10304,13 +10358,13 @@
         <v>167</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>1185</v>
+        <v>1203</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>1186</v>
+        <v>1204</v>
       </c>
       <c r="E171" s="12"/>
       <c r="F171" s="13" cm="1" t="str">
@@ -10318,7 +10372,7 @@
         <v/>
       </c>
       <c r="G171" s="9" cm="1" t="str">
-        <f t="array" ref="G171">IF(F171="","",IF(LEFT(F171,1)="✔",MIN(IF(H171="",1,H171)+1,5),1))</f>
+        <f t="array" ref="G171">IF(F171="","",IF(I171=TODAY(),"done today",IF(LEFT(F171,1)="✔",MIN(IF(H171="",1,H171)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H171" s="14"/>
@@ -10337,13 +10391,13 @@
         <v>168</v>
       </c>
       <c r="B172" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>1185</v>
+        <v>1203</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>1189</v>
+        <v>1207</v>
       </c>
       <c r="E172" s="12"/>
       <c r="F172" s="13" cm="1" t="str">
@@ -10351,7 +10405,7 @@
         <v/>
       </c>
       <c r="G172" s="9" cm="1" t="str">
-        <f t="array" ref="G172">IF(F172="","",IF(LEFT(F172,1)="✔",MIN(IF(H172="",1,H172)+1,5),1))</f>
+        <f t="array" ref="G172">IF(F172="","",IF(I172=TODAY(),"done today",IF(LEFT(F172,1)="✔",MIN(IF(H172="",1,H172)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H172" s="14"/>
@@ -10370,13 +10424,13 @@
         <v>169</v>
       </c>
       <c r="B173" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>1185</v>
+        <v>1203</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>1196</v>
+        <v>1214</v>
       </c>
       <c r="E173" s="12"/>
       <c r="F173" s="13" cm="1" t="str">
@@ -10384,7 +10438,7 @@
         <v/>
       </c>
       <c r="G173" s="9" cm="1" t="str">
-        <f t="array" ref="G173">IF(F173="","",IF(LEFT(F173,1)="✔",MIN(IF(H173="",1,H173)+1,5),1))</f>
+        <f t="array" ref="G173">IF(F173="","",IF(I173=TODAY(),"done today",IF(LEFT(F173,1)="✔",MIN(IF(H173="",1,H173)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H173" s="14"/>
@@ -10403,13 +10457,13 @@
         <v>170</v>
       </c>
       <c r="B174" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>1204</v>
+        <v>1222</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>1205</v>
+        <v>1223</v>
       </c>
       <c r="E174" s="12"/>
       <c r="F174" s="13" cm="1" t="str">
@@ -10417,7 +10471,7 @@
         <v/>
       </c>
       <c r="G174" s="9" cm="1" t="str">
-        <f t="array" ref="G174">IF(F174="","",IF(LEFT(F174,1)="✔",MIN(IF(H174="",1,H174)+1,5),1))</f>
+        <f t="array" ref="G174">IF(F174="","",IF(I174=TODAY(),"done today",IF(LEFT(F174,1)="✔",MIN(IF(H174="",1,H174)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H174" s="14"/>
@@ -10436,13 +10490,13 @@
         <v>171</v>
       </c>
       <c r="B175" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>1204</v>
+        <v>1222</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>1214</v>
+        <v>1232</v>
       </c>
       <c r="E175" s="12"/>
       <c r="F175" s="13" cm="1" t="str">
@@ -10450,7 +10504,7 @@
         <v/>
       </c>
       <c r="G175" s="9" cm="1" t="str">
-        <f t="array" ref="G175">IF(F175="","",IF(LEFT(F175,1)="✔",MIN(IF(H175="",1,H175)+1,5),1))</f>
+        <f t="array" ref="G175">IF(F175="","",IF(I175=TODAY(),"done today",IF(LEFT(F175,1)="✔",MIN(IF(H175="",1,H175)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H175" s="14"/>
@@ -10469,13 +10523,13 @@
         <v>172</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>1204</v>
+        <v>1222</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>1223</v>
+        <v>1241</v>
       </c>
       <c r="E176" s="12"/>
       <c r="F176" s="13" cm="1" t="str">
@@ -10483,7 +10537,7 @@
         <v/>
       </c>
       <c r="G176" s="9" cm="1" t="str">
-        <f t="array" ref="G176">IF(F176="","",IF(LEFT(F176,1)="✔",MIN(IF(H176="",1,H176)+1,5),1))</f>
+        <f t="array" ref="G176">IF(F176="","",IF(I176=TODAY(),"done today",IF(LEFT(F176,1)="✔",MIN(IF(H176="",1,H176)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H176" s="14"/>
@@ -10502,13 +10556,13 @@
         <v>173</v>
       </c>
       <c r="B177" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>1232</v>
+        <v>1250</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>1233</v>
+        <v>1251</v>
       </c>
       <c r="E177" s="12"/>
       <c r="F177" s="13" cm="1" t="str">
@@ -10516,7 +10570,7 @@
         <v/>
       </c>
       <c r="G177" s="9" cm="1" t="str">
-        <f t="array" ref="G177">IF(F177="","",IF(LEFT(F177,1)="✔",MIN(IF(H177="",1,H177)+1,5),1))</f>
+        <f t="array" ref="G177">IF(F177="","",IF(I177=TODAY(),"done today",IF(LEFT(F177,1)="✔",MIN(IF(H177="",1,H177)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H177" s="14"/>
@@ -10535,21 +10589,21 @@
         <v>174</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>1232</v>
+        <v>1250</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>1236</v>
+        <v>1254</v>
       </c>
       <c r="E178" s="12"/>
       <c r="F178" s="13" cm="1" t="str">
-        <f t="array" ref="F178">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$178,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$175:$E$175),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="F178">IFERROR(_xlfn.LET(_xlpm.a,Deck!$E$178,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$175:$J$175),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="G178" s="9" cm="1" t="str">
-        <f t="array" ref="G178">IF(F178="","",IF(LEFT(F178,1)="✔",MIN(IF(H178="",1,H178)+1,5),1))</f>
+        <f t="array" ref="G178">IF(F178="","",IF(I178=TODAY(),"done today",IF(LEFT(F178,1)="✔",MIN(IF(H178="",1,H178)+1,5),1)))</f>
         <v/>
       </c>
       <c r="H178" s="14"/>
@@ -12726,644 +12780,668 @@
       <c r="H59" t="s">
         <v>350</v>
       </c>
+      <c r="I59" t="s">
+        <v>351</v>
+      </c>
+      <c r="J59" t="s">
+        <v>352</v>
+      </c>
+      <c r="K59" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E60" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F60" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G60" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H60" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I60" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J60" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B61" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E61" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B62" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E62" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B63" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E63" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F63" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G63" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="H63" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I63" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J63" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B64" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E64" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F64" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G64" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="H64" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I64" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="J64" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B65" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E65" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F65" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G65" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H65" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I65" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="J65" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B66" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E66" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F66" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B67" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E67" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F67" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G67" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="H67" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="I67" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J67" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B68" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E68" t="s">
-        <v>415</v>
+        <v>418</v>
+      </c>
+      <c r="F68" t="s">
+        <v>419</v>
+      </c>
+      <c r="G68" t="s">
+        <v>420</v>
+      </c>
+      <c r="H68" t="s">
+        <v>421</v>
+      </c>
+      <c r="I68" t="s">
+        <v>422</v>
+      </c>
+      <c r="J68" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B69" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="E69" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="F69" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="G69" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="H69" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="I69" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="J69" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B70" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="E70" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F70" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="G70" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="H70" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="I70" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="J70" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B71" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E71" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F71" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="G71" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="H71" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="I71" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="J71" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E72" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F72" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="G72" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="H72" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="I72" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="J72" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B73" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E73" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F73" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="G73" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="H73" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B74" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="E74" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="F74" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="G74" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="H74" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B75" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="E75" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F75" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="G75" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="H75" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B76" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E76" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="F76" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="G76" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="H76" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B77" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E77" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="F77" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="G77" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="H77" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B78" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="E78" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="F78" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="G78" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="H78" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B79" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E79" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F79" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B80" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E80" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F80" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="81" spans="1:20">
       <c r="A81" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B81" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="E81" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F81" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B82" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E82" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="83" spans="1:20">
       <c r="A83" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="B83" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="E83" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
     </row>
     <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B84" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="E84" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="F84" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="G84" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="H84" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="B85" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="E85" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="F85" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="G85" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="H85" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
     <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B86" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="E86" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="F86" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
     </row>
     <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B87" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="E87" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="F87" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="G87" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="H87" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="I87" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="J87" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="K87" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="L87" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="M87" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="N87" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="O87" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="P87" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="Q87" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="R87" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="S87" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="T87" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B88" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="E88" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F88" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="G88" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="H88" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="I88" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="J88" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K88" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="L88" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="M88" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="N88" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="O88" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="P88" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="Q88" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="R88" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="S88" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="T88" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
     </row>
     <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B89" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="E89" t="s">
         <v>310</v>
@@ -13374,502 +13452,502 @@
     </row>
     <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="B90" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="E90" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="F90" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="G90" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="H90" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="I90" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="J90" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="B91" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="E91" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="B92" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E92" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="F92" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
     </row>
     <row r="93" spans="1:20">
       <c r="A93" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="B93" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="E93" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="F93" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="G93" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="H93" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="I93" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="J93" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
     </row>
     <row r="94" spans="1:20">
       <c r="A94" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="B94" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="E94" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="F94" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="G94" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="H94" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="I94" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="J94" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="95" spans="1:20">
       <c r="A95" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="B95" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="E95" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="F95" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="G95" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="H95" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="I95" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="J95" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="96" spans="1:20">
       <c r="A96" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="B96" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="E96" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="F96" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="G96" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="H96" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="I96" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="J96" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
     </row>
     <row r="97" spans="1:20">
       <c r="A97" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="B97" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="E97" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="F97" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="G97" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="H97" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="I97" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="J97" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
     </row>
     <row r="98" spans="1:20">
       <c r="A98" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B98" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="E98" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="F98" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="G98" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="H98" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="I98" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="J98" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
     </row>
     <row r="99" spans="1:20">
       <c r="A99" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="B99" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="E99" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="F99" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="G99" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="H99" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="I99" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="J99" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
     </row>
     <row r="100" spans="1:20">
       <c r="A100" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="B100" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="E100" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="F100" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="101" spans="1:20">
       <c r="A101" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="B101" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="E101" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F101" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="102" spans="1:20">
       <c r="A102" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="B102" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="E102" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="F102" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="G102" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="H102" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="I102" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
     </row>
     <row r="103" spans="1:20">
       <c r="A103" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="B103" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="E103" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
     </row>
     <row r="104" spans="1:20">
       <c r="A104" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="B104" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E104" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="105" spans="1:20">
       <c r="A105" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="B105" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="E105" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
     </row>
     <row r="106" spans="1:20">
       <c r="A106" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="B106" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="E106" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="F106" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="G106" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
     </row>
     <row r="107" spans="1:20">
       <c r="A107" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="B107" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="E107" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="F107" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="G107" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="H107" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="I107" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="J107" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="K107" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="L107" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="M107" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="N107" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="O107" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="P107" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="Q107" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="R107" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="S107" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="T107" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
     </row>
     <row r="108" spans="1:20">
       <c r="A108" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="B108" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="E108" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
     </row>
     <row r="109" spans="1:20">
       <c r="A109" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="B109" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="E109" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
     </row>
     <row r="110" spans="1:20">
       <c r="A110" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="B110" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="E110" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
     </row>
     <row r="111" spans="1:20">
       <c r="A111" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="B111" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="E111" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
     </row>
     <row r="112" spans="1:20">
       <c r="A112" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="B112" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E112" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
     </row>
     <row r="113" spans="1:20">
       <c r="A113" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="B113" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="E113" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
     </row>
     <row r="114" spans="1:20">
       <c r="A114" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="B114" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="E114" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
     </row>
     <row r="115" spans="1:20">
       <c r="A115" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="B115" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="E115" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
     </row>
     <row r="116" spans="1:20">
       <c r="A116" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="B116" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="E116" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="F116" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
     </row>
     <row r="117" spans="1:20">
       <c r="A117" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="B117" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="E117" t="s">
         <v>334</v>
@@ -13877,1357 +13955,1468 @@
     </row>
     <row r="118" spans="1:20">
       <c r="A118" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="B118" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="E118" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="F118" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
     </row>
     <row r="119" spans="1:20">
       <c r="A119" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="B119" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="E119" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="F119" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="G119" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="H119" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="I119" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="J119" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="K119" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="L119" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="M119" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="N119" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="O119" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="P119" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="Q119" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="R119" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="S119" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="T119" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
     </row>
     <row r="120" spans="1:20">
       <c r="A120" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="B120" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="E120" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="F120" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="G120" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="H120" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="I120" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="J120" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="K120" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="L120" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="M120" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="N120" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="O120" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="P120" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="Q120" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="R120" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="S120" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="T120" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
     </row>
     <row r="121" spans="1:20">
       <c r="A121" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="B121" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="E121" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
     </row>
     <row r="122" spans="1:20">
       <c r="A122" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="B122" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="E122" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="F122" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="G122" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="H122" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="I122" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="J122" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
     </row>
     <row r="123" spans="1:20">
       <c r="A123" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="B123" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="E123" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="F123" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="G123" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
     </row>
     <row r="124" spans="1:20">
       <c r="A124" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="B124" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="E124" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="F124" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="G124" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="H124" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
     </row>
     <row r="125" spans="1:20">
       <c r="A125" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="B125" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="E125" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F125" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="126" spans="1:20">
       <c r="A126" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="B126" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="E126" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="F126" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="G126" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="H126" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="I126" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="J126" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
     </row>
     <row r="127" spans="1:20">
       <c r="A127" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="B127" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="E127" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="F127" t="s">
-        <v>853</v>
+        <v>861</v>
+      </c>
+      <c r="G127" t="s">
+        <v>862</v>
+      </c>
+      <c r="H127" t="s">
+        <v>863</v>
+      </c>
+      <c r="I127" t="s">
+        <v>864</v>
+      </c>
+      <c r="J127" t="s">
+        <v>865</v>
+      </c>
+      <c r="K127" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="128" spans="1:20">
       <c r="A128" t="s">
-        <v>855</v>
+        <v>868</v>
       </c>
       <c r="B128" t="s">
-        <v>856</v>
+        <v>869</v>
       </c>
       <c r="E128" t="s">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="F128" t="s">
-        <v>858</v>
+        <v>871</v>
       </c>
       <c r="G128" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="H128" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="I128" t="s">
-        <v>861</v>
+        <v>874</v>
       </c>
       <c r="J128" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
       <c r="A129" t="s">
-        <v>865</v>
+        <v>878</v>
       </c>
       <c r="B129" t="s">
-        <v>866</v>
+        <v>879</v>
       </c>
       <c r="E129" t="s">
-        <v>867</v>
+        <v>880</v>
       </c>
       <c r="F129" t="s">
-        <v>868</v>
+        <v>881</v>
       </c>
       <c r="G129" t="s">
-        <v>869</v>
+        <v>882</v>
       </c>
       <c r="H129" t="s">
-        <v>870</v>
+        <v>883</v>
       </c>
       <c r="I129" t="s">
-        <v>871</v>
+        <v>884</v>
       </c>
       <c r="J129" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
       <c r="A130" t="s">
-        <v>874</v>
+        <v>887</v>
       </c>
       <c r="B130" t="s">
-        <v>875</v>
+        <v>888</v>
       </c>
       <c r="E130" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10">
+        <v>880</v>
+      </c>
+      <c r="F130" t="s">
+        <v>881</v>
+      </c>
+      <c r="G130" t="s">
+        <v>882</v>
+      </c>
+      <c r="H130" t="s">
+        <v>889</v>
+      </c>
+      <c r="I130" t="s">
+        <v>890</v>
+      </c>
+      <c r="J130" t="s">
+        <v>891</v>
+      </c>
+      <c r="K130" t="s">
+        <v>883</v>
+      </c>
+      <c r="L130" t="s">
+        <v>884</v>
+      </c>
+      <c r="M130" t="s">
+        <v>885</v>
+      </c>
+      <c r="N130" t="s">
+        <v>892</v>
+      </c>
+      <c r="O130" t="s">
+        <v>893</v>
+      </c>
+      <c r="P130" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
       <c r="A131" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="B131" t="s">
-        <v>878</v>
+        <v>897</v>
       </c>
       <c r="E131" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="F131" t="s">
-        <v>880</v>
+        <v>890</v>
       </c>
       <c r="G131" t="s">
-        <v>881</v>
+        <v>891</v>
       </c>
       <c r="H131" t="s">
-        <v>882</v>
+        <v>892</v>
       </c>
       <c r="I131" t="s">
-        <v>883</v>
+        <v>893</v>
       </c>
       <c r="J131" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
       <c r="A132" t="s">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="B132" t="s">
-        <v>887</v>
+        <v>900</v>
       </c>
       <c r="E132" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
+      <c r="A133" t="s">
+        <v>904</v>
+      </c>
+      <c r="B133" t="s">
+        <v>905</v>
+      </c>
+      <c r="E133" t="s">
+        <v>906</v>
+      </c>
+      <c r="F133" t="s">
+        <v>907</v>
+      </c>
+      <c r="G133" t="s">
+        <v>908</v>
+      </c>
+      <c r="H133" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134" t="s">
+        <v>911</v>
+      </c>
+      <c r="B134" t="s">
+        <v>912</v>
+      </c>
+      <c r="E134" t="s">
+        <v>913</v>
+      </c>
+      <c r="F134" t="s">
+        <v>914</v>
+      </c>
+      <c r="G134" t="s">
+        <v>915</v>
+      </c>
+      <c r="H134" t="s">
+        <v>916</v>
+      </c>
+      <c r="I134" t="s">
+        <v>917</v>
+      </c>
+      <c r="J134" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135" t="s">
+        <v>921</v>
+      </c>
+      <c r="B135" t="s">
+        <v>922</v>
+      </c>
+      <c r="E135" t="s">
+        <v>923</v>
+      </c>
+      <c r="F135" t="s">
+        <v>924</v>
+      </c>
+      <c r="G135" t="s">
+        <v>925</v>
+      </c>
+      <c r="H135" t="s">
+        <v>926</v>
+      </c>
+      <c r="I135" t="s">
+        <v>927</v>
+      </c>
+      <c r="J135" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
+      <c r="A136" t="s">
+        <v>930</v>
+      </c>
+      <c r="B136" t="s">
+        <v>931</v>
+      </c>
+      <c r="E136" t="s">
+        <v>932</v>
+      </c>
+      <c r="F136" t="s">
+        <v>933</v>
+      </c>
+      <c r="G136" t="s">
+        <v>934</v>
+      </c>
+      <c r="H136" t="s">
+        <v>935</v>
+      </c>
+      <c r="I136" t="s">
+        <v>936</v>
+      </c>
+      <c r="J136" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
+      <c r="A137" t="s">
+        <v>939</v>
+      </c>
+      <c r="B137" t="s">
+        <v>940</v>
+      </c>
+      <c r="E137" t="s">
+        <v>941</v>
+      </c>
+      <c r="F137" t="s">
+        <v>942</v>
+      </c>
+      <c r="G137" t="s">
+        <v>943</v>
+      </c>
+      <c r="H137" t="s">
+        <v>944</v>
+      </c>
+      <c r="I137" t="s">
+        <v>945</v>
+      </c>
+      <c r="J137" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
+      <c r="A138" t="s">
+        <v>948</v>
+      </c>
+      <c r="B138" t="s">
+        <v>678</v>
+      </c>
+      <c r="E138" t="s">
+        <v>679</v>
+      </c>
+      <c r="F138" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
+      <c r="A139" t="s">
+        <v>950</v>
+      </c>
+      <c r="B139" t="s">
+        <v>951</v>
+      </c>
+      <c r="E139" t="s">
+        <v>952</v>
+      </c>
+      <c r="F139" t="s">
+        <v>953</v>
+      </c>
+      <c r="G139" t="s">
+        <v>954</v>
+      </c>
+      <c r="H139" t="s">
+        <v>955</v>
+      </c>
+      <c r="I139" t="s">
+        <v>956</v>
+      </c>
+      <c r="J139" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
+      <c r="A140" t="s">
+        <v>960</v>
+      </c>
+      <c r="B140" t="s">
+        <v>961</v>
+      </c>
+      <c r="E140" t="s">
+        <v>962</v>
+      </c>
+      <c r="F140" t="s">
+        <v>963</v>
+      </c>
+      <c r="G140" t="s">
+        <v>964</v>
+      </c>
+      <c r="H140" t="s">
+        <v>965</v>
+      </c>
+      <c r="I140" t="s">
+        <v>966</v>
+      </c>
+      <c r="J140" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
+      <c r="A141" t="s">
+        <v>969</v>
+      </c>
+      <c r="B141" t="s">
+        <v>970</v>
+      </c>
+      <c r="E141" t="s">
+        <v>971</v>
+      </c>
+      <c r="F141" t="s">
+        <v>972</v>
+      </c>
+      <c r="G141" t="s">
+        <v>973</v>
+      </c>
+      <c r="H141" t="s">
+        <v>974</v>
+      </c>
+      <c r="I141" t="s">
+        <v>975</v>
+      </c>
+      <c r="J141" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142" t="s">
+        <v>978</v>
+      </c>
+      <c r="B142" t="s">
+        <v>979</v>
+      </c>
+      <c r="E142" t="s">
+        <v>980</v>
+      </c>
+      <c r="F142" t="s">
+        <v>981</v>
+      </c>
+      <c r="G142" t="s">
+        <v>982</v>
+      </c>
+      <c r="H142" t="s">
+        <v>983</v>
+      </c>
+      <c r="I142" t="s">
+        <v>984</v>
+      </c>
+      <c r="J142" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143" t="s">
+        <v>987</v>
+      </c>
+      <c r="B143" t="s">
+        <v>988</v>
+      </c>
+      <c r="E143" t="s">
+        <v>989</v>
+      </c>
+      <c r="F143" t="s">
+        <v>990</v>
+      </c>
+      <c r="G143" t="s">
+        <v>991</v>
+      </c>
+      <c r="H143" t="s">
+        <v>992</v>
+      </c>
+      <c r="I143" t="s">
+        <v>993</v>
+      </c>
+      <c r="J143" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
+      <c r="A144" t="s">
+        <v>996</v>
+      </c>
+      <c r="B144" t="s">
+        <v>997</v>
+      </c>
+      <c r="E144" t="s">
+        <v>998</v>
+      </c>
+      <c r="F144" t="s">
+        <v>999</v>
+      </c>
+      <c r="G144" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H144" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I144" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J144" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
+      <c r="A145" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E145" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F145" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G145" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H145" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I145" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J145" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
+      <c r="A146" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B146" t="s">
         <v>888</v>
       </c>
-    </row>
-    <row r="133" spans="1:10">
-      <c r="A133" t="s">
-        <v>891</v>
-      </c>
-      <c r="B133" t="s">
-        <v>892</v>
-      </c>
-      <c r="E133" t="s">
-        <v>893</v>
-      </c>
-      <c r="F133" t="s">
-        <v>894</v>
-      </c>
-      <c r="G133" t="s">
-        <v>895</v>
-      </c>
-      <c r="H133" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10">
-      <c r="A134" t="s">
-        <v>898</v>
-      </c>
-      <c r="B134" t="s">
-        <v>899</v>
-      </c>
-      <c r="E134" t="s">
-        <v>900</v>
-      </c>
-      <c r="F134" t="s">
-        <v>901</v>
-      </c>
-      <c r="G134" t="s">
-        <v>902</v>
-      </c>
-      <c r="H134" t="s">
-        <v>903</v>
-      </c>
-      <c r="I134" t="s">
-        <v>904</v>
-      </c>
-      <c r="J134" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10">
-      <c r="A135" t="s">
-        <v>908</v>
-      </c>
-      <c r="B135" t="s">
-        <v>909</v>
-      </c>
-      <c r="E135" t="s">
-        <v>910</v>
-      </c>
-      <c r="F135" t="s">
-        <v>911</v>
-      </c>
-      <c r="G135" t="s">
-        <v>912</v>
-      </c>
-      <c r="H135" t="s">
-        <v>913</v>
-      </c>
-      <c r="I135" t="s">
-        <v>914</v>
-      </c>
-      <c r="J135" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10">
-      <c r="A136" t="s">
-        <v>917</v>
-      </c>
-      <c r="B136" t="s">
-        <v>918</v>
-      </c>
-      <c r="E136" t="s">
-        <v>919</v>
-      </c>
-      <c r="F136" t="s">
-        <v>920</v>
-      </c>
-      <c r="G136" t="s">
-        <v>921</v>
-      </c>
-      <c r="H136" t="s">
-        <v>922</v>
-      </c>
-      <c r="I136" t="s">
-        <v>923</v>
-      </c>
-      <c r="J136" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10">
-      <c r="A137" t="s">
-        <v>926</v>
-      </c>
-      <c r="B137" t="s">
-        <v>927</v>
-      </c>
-      <c r="E137" t="s">
-        <v>928</v>
-      </c>
-      <c r="F137" t="s">
-        <v>929</v>
-      </c>
-      <c r="G137" t="s">
-        <v>930</v>
-      </c>
-      <c r="H137" t="s">
-        <v>931</v>
-      </c>
-      <c r="I137" t="s">
-        <v>932</v>
-      </c>
-      <c r="J137" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10">
-      <c r="A138" t="s">
-        <v>935</v>
-      </c>
-      <c r="B138" t="s">
-        <v>670</v>
-      </c>
-      <c r="E138" t="s">
-        <v>671</v>
-      </c>
-      <c r="F138" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10">
-      <c r="A139" t="s">
-        <v>937</v>
-      </c>
-      <c r="B139" t="s">
-        <v>938</v>
-      </c>
-      <c r="E139" t="s">
-        <v>939</v>
-      </c>
-      <c r="F139" t="s">
-        <v>940</v>
-      </c>
-      <c r="G139" t="s">
-        <v>941</v>
-      </c>
-      <c r="H139" t="s">
-        <v>942</v>
-      </c>
-      <c r="I139" t="s">
-        <v>943</v>
-      </c>
-      <c r="J139" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10">
-      <c r="A140" t="s">
-        <v>947</v>
-      </c>
-      <c r="B140" t="s">
-        <v>948</v>
-      </c>
-      <c r="E140" t="s">
-        <v>949</v>
-      </c>
-      <c r="F140" t="s">
-        <v>950</v>
-      </c>
-      <c r="G140" t="s">
-        <v>951</v>
-      </c>
-      <c r="H140" t="s">
-        <v>952</v>
-      </c>
-      <c r="I140" t="s">
-        <v>953</v>
-      </c>
-      <c r="J140" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10">
-      <c r="A141" t="s">
-        <v>956</v>
-      </c>
-      <c r="B141" t="s">
-        <v>957</v>
-      </c>
-      <c r="E141" t="s">
-        <v>958</v>
-      </c>
-      <c r="F141" t="s">
-        <v>959</v>
-      </c>
-      <c r="G141" t="s">
-        <v>960</v>
-      </c>
-      <c r="H141" t="s">
-        <v>961</v>
-      </c>
-      <c r="I141" t="s">
-        <v>962</v>
-      </c>
-      <c r="J141" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10">
-      <c r="A142" t="s">
-        <v>965</v>
-      </c>
-      <c r="B142" t="s">
-        <v>966</v>
-      </c>
-      <c r="E142" t="s">
-        <v>967</v>
-      </c>
-      <c r="F142" t="s">
-        <v>968</v>
-      </c>
-      <c r="G142" t="s">
-        <v>969</v>
-      </c>
-      <c r="H142" t="s">
-        <v>970</v>
-      </c>
-      <c r="I142" t="s">
-        <v>971</v>
-      </c>
-      <c r="J142" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10">
-      <c r="A143" t="s">
-        <v>974</v>
-      </c>
-      <c r="B143" t="s">
-        <v>975</v>
-      </c>
-      <c r="E143" t="s">
-        <v>976</v>
-      </c>
-      <c r="F143" t="s">
-        <v>977</v>
-      </c>
-      <c r="G143" t="s">
-        <v>978</v>
-      </c>
-      <c r="H143" t="s">
-        <v>979</v>
-      </c>
-      <c r="I143" t="s">
-        <v>980</v>
-      </c>
-      <c r="J143" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10">
-      <c r="A144" t="s">
-        <v>983</v>
-      </c>
-      <c r="B144" t="s">
-        <v>984</v>
-      </c>
-      <c r="E144" t="s">
-        <v>985</v>
-      </c>
-      <c r="F144" t="s">
-        <v>986</v>
-      </c>
-      <c r="G144" t="s">
-        <v>987</v>
-      </c>
-      <c r="H144" t="s">
-        <v>988</v>
-      </c>
-      <c r="I144" t="s">
-        <v>989</v>
-      </c>
-      <c r="J144" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
-      <c r="A145" t="s">
-        <v>993</v>
-      </c>
-      <c r="B145" t="s">
-        <v>994</v>
-      </c>
-      <c r="E145" t="s">
-        <v>995</v>
-      </c>
-      <c r="F145" t="s">
-        <v>996</v>
-      </c>
-      <c r="G145" t="s">
-        <v>997</v>
-      </c>
-      <c r="H145" t="s">
+      <c r="E146" t="s">
         <v>998</v>
       </c>
-      <c r="I145" t="s">
+      <c r="F146" t="s">
         <v>999</v>
       </c>
-      <c r="J145" t="s">
+      <c r="G146" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="146" spans="1:10">
-      <c r="A146" t="s">
+      <c r="H146" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I146" t="s">
+        <v>1009</v>
+      </c>
+      <c r="J146" t="s">
+        <v>1010</v>
+      </c>
+      <c r="K146" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L146" t="s">
         <v>1002</v>
       </c>
-      <c r="B146" t="s">
-        <v>875</v>
-      </c>
-      <c r="E146" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10">
+      <c r="M146" t="s">
+        <v>1003</v>
+      </c>
+      <c r="N146" t="s">
+        <v>1011</v>
+      </c>
+      <c r="O146" t="s">
+        <v>1012</v>
+      </c>
+      <c r="P146" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
       <c r="A147" t="s">
-        <v>1004</v>
+        <v>1017</v>
       </c>
       <c r="B147" t="s">
-        <v>1005</v>
+        <v>1018</v>
       </c>
       <c r="E147" t="s">
-        <v>1006</v>
+        <v>1019</v>
       </c>
       <c r="F147" t="s">
-        <v>1007</v>
+        <v>1020</v>
       </c>
       <c r="G147" t="s">
-        <v>1008</v>
+        <v>1021</v>
       </c>
       <c r="H147" t="s">
-        <v>1009</v>
+        <v>1022</v>
       </c>
       <c r="I147" t="s">
-        <v>1010</v>
+        <v>1023</v>
       </c>
       <c r="J147" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
       <c r="A148" t="s">
-        <v>1014</v>
+        <v>1027</v>
       </c>
       <c r="B148" t="s">
-        <v>1015</v>
+        <v>1028</v>
       </c>
       <c r="E148" t="s">
-        <v>1016</v>
+        <v>1029</v>
       </c>
       <c r="F148" t="s">
-        <v>1017</v>
+        <v>1030</v>
       </c>
       <c r="G148" t="s">
-        <v>1018</v>
+        <v>1031</v>
       </c>
       <c r="H148" t="s">
-        <v>1019</v>
+        <v>1032</v>
       </c>
       <c r="I148" t="s">
-        <v>1020</v>
+        <v>1033</v>
       </c>
       <c r="J148" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
       <c r="A149" t="s">
-        <v>1023</v>
+        <v>1036</v>
       </c>
       <c r="B149" t="s">
-        <v>1024</v>
+        <v>1037</v>
       </c>
       <c r="E149" t="s">
-        <v>1025</v>
+        <v>1038</v>
       </c>
       <c r="F149" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="G149" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="H149" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="I149" t="s">
-        <v>1029</v>
+        <v>1042</v>
       </c>
       <c r="J149" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16">
       <c r="A150" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="B150" t="s">
-        <v>1033</v>
+        <v>1046</v>
       </c>
       <c r="E150" t="s">
-        <v>1034</v>
+        <v>1047</v>
       </c>
       <c r="F150" t="s">
-        <v>1035</v>
+        <v>1048</v>
       </c>
       <c r="G150" t="s">
-        <v>1036</v>
+        <v>1049</v>
       </c>
       <c r="H150" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="I150" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
       <c r="J150" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
       <c r="A151" t="s">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="B151" t="s">
         <v>134</v>
       </c>
       <c r="E151" t="s">
-        <v>1044</v>
+        <v>1057</v>
       </c>
       <c r="F151" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="G151" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H151" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I151" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J151" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
+      <c r="A152" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E152" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G152" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H152" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I152" t="s">
+        <v>1069</v>
+      </c>
+      <c r="J152" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
+      <c r="A153" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E153" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G153" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H153" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I153" t="s">
+        <v>1077</v>
+      </c>
+      <c r="J153" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16">
+      <c r="A154" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B154" t="s">
         <v>1046</v>
       </c>
-      <c r="H151" t="s">
-        <v>1047</v>
-      </c>
-      <c r="I151" t="s">
-        <v>1048</v>
-      </c>
-      <c r="J151" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10">
-      <c r="A152" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B152" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E152" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F152" t="s">
-        <v>1053</v>
-      </c>
-      <c r="G152" t="s">
-        <v>1054</v>
-      </c>
-      <c r="H152" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I152" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J152" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10">
-      <c r="A153" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B153" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E153" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F153" t="s">
-        <v>1061</v>
-      </c>
-      <c r="G153" t="s">
-        <v>1062</v>
-      </c>
-      <c r="H153" t="s">
-        <v>1063</v>
-      </c>
-      <c r="I153" t="s">
-        <v>1064</v>
-      </c>
-      <c r="J153" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10">
-      <c r="A154" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B154" t="s">
-        <v>1033</v>
-      </c>
       <c r="E154" t="s">
-        <v>1068</v>
+        <v>1081</v>
       </c>
       <c r="F154" t="s">
-        <v>1069</v>
+        <v>1082</v>
       </c>
       <c r="G154" t="s">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="H154" t="s">
-        <v>1071</v>
+        <v>1084</v>
       </c>
       <c r="I154" t="s">
-        <v>1072</v>
+        <v>1085</v>
       </c>
       <c r="J154" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16">
       <c r="A155" t="s">
-        <v>1075</v>
+        <v>1088</v>
       </c>
       <c r="B155" t="s">
         <v>134</v>
       </c>
       <c r="E155" t="s">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="F155" t="s">
-        <v>1077</v>
+        <v>1090</v>
       </c>
       <c r="G155" t="s">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="H155" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="I155" t="s">
-        <v>1080</v>
+        <v>1093</v>
       </c>
       <c r="J155" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16">
       <c r="A156" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="B156" t="s">
-        <v>1084</v>
+        <v>1097</v>
       </c>
       <c r="E156" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="F156" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="G156" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="H156" t="s">
-        <v>1088</v>
+        <v>1101</v>
       </c>
       <c r="I156" t="s">
-        <v>1089</v>
+        <v>1102</v>
       </c>
       <c r="J156" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16">
       <c r="A157" t="s">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="B157" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="E157" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="F157" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16">
       <c r="A158" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
       <c r="B158" t="s">
-        <v>1099</v>
+        <v>1112</v>
       </c>
       <c r="E158" t="s">
-        <v>1100</v>
+        <v>1113</v>
       </c>
       <c r="F158" t="s">
-        <v>1101</v>
+        <v>1114</v>
       </c>
       <c r="G158" t="s">
-        <v>1102</v>
+        <v>1115</v>
       </c>
       <c r="H158" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16">
       <c r="A159" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="B159" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="E159" t="s">
-        <v>1107</v>
+        <v>1120</v>
       </c>
       <c r="F159" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
       <c r="G159" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="H159" t="s">
-        <v>1110</v>
+        <v>1123</v>
       </c>
       <c r="I159" t="s">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="J159" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16">
       <c r="A160" t="s">
-        <v>1114</v>
+        <v>1127</v>
       </c>
       <c r="B160" t="s">
-        <v>1115</v>
+        <v>1128</v>
       </c>
       <c r="E160" t="s">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="F160" t="s">
-        <v>1117</v>
+        <v>1130</v>
       </c>
       <c r="G160" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="H160" t="s">
-        <v>1119</v>
+        <v>1132</v>
       </c>
       <c r="I160" t="s">
-        <v>1120</v>
+        <v>1133</v>
       </c>
       <c r="J160" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>1124</v>
+        <v>1137</v>
       </c>
       <c r="B161" t="s">
-        <v>1125</v>
+        <v>1138</v>
       </c>
       <c r="E161" t="s">
-        <v>1126</v>
+        <v>1139</v>
       </c>
       <c r="F161" t="s">
-        <v>1127</v>
+        <v>1140</v>
       </c>
       <c r="G161" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="H161" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="I161" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="J161" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="B162" t="s">
-        <v>1134</v>
+        <v>1147</v>
       </c>
       <c r="E162" t="s">
-        <v>1135</v>
+        <v>1148</v>
       </c>
       <c r="F162" t="s">
-        <v>1136</v>
+        <v>1149</v>
       </c>
       <c r="G162" t="s">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="H162" t="s">
-        <v>1138</v>
+        <v>1151</v>
       </c>
       <c r="I162" t="s">
-        <v>1139</v>
+        <v>1152</v>
       </c>
       <c r="J162" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>1142</v>
+        <v>1155</v>
       </c>
       <c r="B163" t="s">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="E163" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
       <c r="F163" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="G163" t="s">
-        <v>1146</v>
+        <v>1159</v>
       </c>
       <c r="H163" t="s">
-        <v>1147</v>
+        <v>1160</v>
       </c>
       <c r="I163" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="J163" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>1151</v>
+        <v>1164</v>
       </c>
       <c r="B164" t="s">
-        <v>1152</v>
+        <v>1165</v>
       </c>
       <c r="E164" t="s">
-        <v>1153</v>
+        <v>1166</v>
       </c>
       <c r="F164" t="s">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="G164" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12">
       <c r="A165" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="B165" t="s">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="E165" t="s">
-        <v>1161</v>
+        <v>1174</v>
       </c>
       <c r="F165" t="s">
-        <v>1162</v>
+        <v>1175</v>
       </c>
       <c r="G165" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10">
+        <v>1176</v>
+      </c>
+      <c r="H165" t="s">
+        <v>1177</v>
+      </c>
+      <c r="I165" t="s">
+        <v>1178</v>
+      </c>
+      <c r="J165" t="s">
+        <v>1166</v>
+      </c>
+      <c r="K165" t="s">
+        <v>1179</v>
+      </c>
+      <c r="L165" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12">
       <c r="A166" t="s">
-        <v>1164</v>
+        <v>1182</v>
       </c>
       <c r="B166" t="s">
-        <v>1165</v>
+        <v>1183</v>
       </c>
       <c r="E166" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12">
       <c r="A167" t="s">
-        <v>1168</v>
+        <v>1186</v>
       </c>
       <c r="B167" t="s">
-        <v>1169</v>
+        <v>1187</v>
       </c>
       <c r="E167" t="s">
-        <v>1170</v>
+        <v>1188</v>
       </c>
       <c r="F167" t="s">
-        <v>1171</v>
+        <v>1189</v>
       </c>
       <c r="G167" t="s">
-        <v>1172</v>
+        <v>1190</v>
       </c>
       <c r="H167" t="s">
-        <v>1173</v>
+        <v>1191</v>
       </c>
       <c r="I167" t="s">
-        <v>1174</v>
+        <v>1192</v>
       </c>
       <c r="J167" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12">
       <c r="A168" t="s">
-        <v>1177</v>
+        <v>1195</v>
       </c>
       <c r="B168" t="s">
-        <v>1178</v>
+        <v>1196</v>
       </c>
       <c r="E168" t="s">
-        <v>1179</v>
+        <v>1197</v>
       </c>
       <c r="F168" t="s">
-        <v>1180</v>
+        <v>1198</v>
       </c>
       <c r="G168" t="s">
-        <v>1181</v>
+        <v>1199</v>
       </c>
       <c r="H168" t="s">
-        <v>1182</v>
+        <v>1200</v>
       </c>
       <c r="I168" t="s">
-        <v>1183</v>
+        <v>1201</v>
       </c>
       <c r="J168" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12">
       <c r="A169" t="s">
-        <v>1187</v>
+        <v>1205</v>
       </c>
       <c r="B169" t="s">
-        <v>1188</v>
+        <v>1206</v>
       </c>
       <c r="E169" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="F169" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>1190</v>
+        <v>1208</v>
       </c>
       <c r="B170" t="s">
-        <v>1191</v>
+        <v>1209</v>
       </c>
       <c r="E170" t="s">
-        <v>1192</v>
+        <v>1210</v>
       </c>
       <c r="F170" t="s">
-        <v>1193</v>
+        <v>1211</v>
       </c>
       <c r="G170" t="s">
-        <v>1194</v>
+        <v>1212</v>
       </c>
       <c r="H170" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12">
       <c r="A171" t="s">
-        <v>1197</v>
+        <v>1215</v>
       </c>
       <c r="B171" t="s">
-        <v>1015</v>
+        <v>1028</v>
       </c>
       <c r="E171" t="s">
-        <v>1198</v>
+        <v>1216</v>
       </c>
       <c r="F171" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="G171" t="s">
-        <v>1200</v>
+        <v>1218</v>
       </c>
       <c r="H171" t="s">
-        <v>1201</v>
+        <v>1219</v>
       </c>
       <c r="I171" t="s">
-        <v>1202</v>
+        <v>1220</v>
       </c>
       <c r="J171" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12">
       <c r="A172" t="s">
-        <v>1206</v>
+        <v>1224</v>
       </c>
       <c r="B172" t="s">
-        <v>1207</v>
+        <v>1225</v>
       </c>
       <c r="E172" t="s">
-        <v>1208</v>
+        <v>1226</v>
       </c>
       <c r="F172" t="s">
-        <v>1209</v>
+        <v>1227</v>
       </c>
       <c r="G172" t="s">
-        <v>1210</v>
+        <v>1228</v>
       </c>
       <c r="H172" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
       <c r="I172" t="s">
-        <v>1212</v>
+        <v>1230</v>
       </c>
       <c r="J172" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12">
       <c r="A173" t="s">
-        <v>1215</v>
+        <v>1233</v>
       </c>
       <c r="B173" t="s">
-        <v>1216</v>
+        <v>1234</v>
       </c>
       <c r="E173" t="s">
-        <v>1217</v>
+        <v>1235</v>
       </c>
       <c r="F173" t="s">
-        <v>1218</v>
+        <v>1236</v>
       </c>
       <c r="G173" t="s">
-        <v>1219</v>
+        <v>1237</v>
       </c>
       <c r="H173" t="s">
-        <v>1220</v>
+        <v>1238</v>
       </c>
       <c r="I173" t="s">
-        <v>1221</v>
+        <v>1239</v>
       </c>
       <c r="J173" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12">
       <c r="A174" t="s">
-        <v>1224</v>
+        <v>1242</v>
       </c>
       <c r="B174" t="s">
-        <v>1225</v>
+        <v>1243</v>
       </c>
       <c r="E174" t="s">
-        <v>1226</v>
+        <v>1244</v>
       </c>
       <c r="F174" t="s">
-        <v>1227</v>
+        <v>1245</v>
       </c>
       <c r="G174" t="s">
-        <v>1228</v>
+        <v>1246</v>
       </c>
       <c r="H174" t="s">
-        <v>1229</v>
+        <v>1247</v>
       </c>
       <c r="I174" t="s">
-        <v>1230</v>
+        <v>1248</v>
       </c>
       <c r="J174" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12">
       <c r="A175" t="s">
-        <v>1234</v>
+        <v>1252</v>
       </c>
       <c r="B175" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E175" t="s">
         <v>1235</v>
       </c>
-      <c r="E175" t="s">
-        <v>1220</v>
+      <c r="F175" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G175" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H175" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I175" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J175" t="s">
+        <v>1240</v>
       </c>
     </row>
   </sheetData>
